--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -285,7 +285,7 @@
     <t>Total SCHOOL CHOICE / CHOICE FUNDING</t>
   </si>
   <si>
-    <t>GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>PHILANTHROPY</t>
   </si>
   <si>
     <t>Foundation Grant</t>
@@ -294,7 +294,7 @@
     <t>Annual Fund</t>
   </si>
   <si>
-    <t>Total GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>Total PHILANTHROPY</t>
   </si>
   <si>
     <t>OTHER REVENUE</t>
@@ -583,7 +583,7 @@
     </font>
     <font>
       <color rgb="FF94A3B8"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -627,7 +627,7 @@
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -651,7 +651,7 @@
     <font>
       <i/>
       <color rgb="FF888888"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1674,25 +1674,25 @@
       <c r="A16" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="27" t="str">
         <f>SUM(B14:B15)</f>
-        <v>75000</v>
-      </c>
-      <c r="C16" s="27">
+        <v>0</v>
+      </c>
+      <c r="C16" s="27" t="str">
         <f>SUM(C14:C15)</f>
-        <v>70000</v>
-      </c>
-      <c r="D16" s="27">
+        <v>0</v>
+      </c>
+      <c r="D16" s="27" t="str">
         <f>SUM(D14:D15)</f>
-        <v>65000</v>
-      </c>
-      <c r="E16" s="27">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27" t="str">
         <f>SUM(E14:E15)</f>
-        <v>60000</v>
-      </c>
-      <c r="F16" s="27">
+        <v>0</v>
+      </c>
+      <c r="F16" s="27" t="str">
         <f>SUM(F14:F15)</f>
-        <v>55000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -108,7 +108,7 @@
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Assumptions</t>
+    <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -309,7 +309,7 @@
     <t>TOTAL NET REVENUE</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Staffing &amp; Personnel</t>
+    <t>SchoolStack Budget - Staffing &amp; Personnel</t>
   </si>
   <si>
     <t>Role</t>
@@ -504,7 +504,7 @@
     <t>Enrollment Growth %</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>KEY RATIOS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -561,7 +561,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -637,6 +637,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -655,7 +665,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -674,11 +684,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -711,6 +726,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -729,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -750,11 +774,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -764,13 +789,15 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1341,7 +1368,7 @@
       <c r="A32" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="24" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1371,22 +1398,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1394,23 +1421,23 @@
       <c r="A2" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>100</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>130</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>160</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>185</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>200</v>
       </c>
@@ -1429,23 +1456,23 @@
       <c r="A4" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>10500*Assumptions!B22</f>
         <v>1050000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>10815*Assumptions!B23</f>
         <v>1405950</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>11140*Assumptions!B24</f>
         <v>1782400</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>11474*Assumptions!B25</f>
         <v>2122690</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>11818*Assumptions!B26</f>
         <v>2363600</v>
       </c>
@@ -1454,23 +1481,23 @@
       <c r="A5" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>350*Assumptions!B22</f>
         <v>35000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>350*Assumptions!B23</f>
         <v>45500</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>350*Assumptions!B24</f>
         <v>56000</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>350*Assumptions!B25</f>
         <v>64750</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>350*Assumptions!B26</f>
         <v>70000</v>
       </c>
@@ -1479,23 +1506,23 @@
       <c r="A6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>SUM(B4:B5)</f>
         <v>1085000</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>SUM(C4:C5)</f>
         <v>1451450</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>SUM(D4:D5)</f>
         <v>1838400</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>SUM(E4:E5)</f>
         <v>2187440</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>SUM(F4:F5)</f>
         <v>2433600</v>
       </c>
@@ -1514,23 +1541,23 @@
       <c r="A8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>--1050*Assumptions!B22</f>
         <v>-105000</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>--1082*Assumptions!B23</f>
         <v>-140660</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>--1114*Assumptions!B24</f>
         <v>-178240</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>--1147*Assumptions!B25</f>
         <v>-212195</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>--1182*Assumptions!B26</f>
         <v>-236400</v>
       </c>
@@ -1539,23 +1566,23 @@
       <c r="A9" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <f>SUM(B8:B8)</f>
         <v>-105000</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <f>SUM(C8:C8)</f>
         <v>-140660</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>SUM(D8:D8)</f>
         <v>-178240</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <f>SUM(E8:E8)</f>
         <v>-212195</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <f>SUM(F8:F8)</f>
         <v>-236400</v>
       </c>
@@ -1574,23 +1601,23 @@
       <c r="A11" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>8700*Assumptions!B22</f>
         <v>870000</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>8961*Assumptions!B23</f>
         <v>1164930</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>9230*Assumptions!B24</f>
         <v>1476800</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>9507*Assumptions!B25</f>
         <v>1758795</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>9792*Assumptions!B26</f>
         <v>1958400</v>
       </c>
@@ -1599,23 +1626,23 @@
       <c r="A12" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <f>SUM(B11:B11)</f>
         <v>870000</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <f>SUM(C11:C11)</f>
         <v>1164930</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>SUM(D11:D11)</f>
         <v>1476800</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <f>SUM(E11:E11)</f>
         <v>1758795</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <f>SUM(F11:F11)</f>
         <v>1958400</v>
       </c>
@@ -1634,19 +1661,19 @@
       <c r="A14" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <v>50000</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <v>40000</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <v>30000</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <v>20000</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <v>10000</v>
       </c>
     </row>
@@ -1654,19 +1681,19 @@
       <c r="A15" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <v>25000</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <v>30000</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <v>35000</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <v>40000</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <v>45000</v>
       </c>
     </row>
@@ -1674,23 +1701,23 @@
       <c r="A16" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="27" t="str">
+      <c r="B16" s="28" t="str">
         <f>SUM(B14:B15)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="27" t="str">
+      <c r="C16" s="28" t="str">
         <f>SUM(C14:C15)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="27" t="str">
+      <c r="D16" s="28" t="str">
         <f>SUM(D14:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="27" t="str">
+      <c r="E16" s="28" t="str">
         <f>SUM(E14:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="27" t="str">
+      <c r="F16" s="28" t="str">
         <f>SUM(F14:F15)</f>
         <v>0</v>
       </c>
@@ -1709,23 +1736,23 @@
       <c r="A18" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <f>500*Assumptions!B22</f>
         <v>50000</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <f>515*Assumptions!B23</f>
         <v>66950</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>530*Assumptions!B24</f>
         <v>84800</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>546*Assumptions!B25</f>
         <v>101010</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <f>562*Assumptions!B26</f>
         <v>112400</v>
       </c>
@@ -1734,23 +1761,23 @@
       <c r="A19" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="28">
         <f>SUM(B18:B18)</f>
         <v>50000</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>SUM(C18:C18)</f>
         <v>66950</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>SUM(D18:D18)</f>
         <v>84800</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>SUM(E18:E18)</f>
         <v>101010</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <f>SUM(F18:F18)</f>
         <v>112400</v>
       </c>
@@ -1759,23 +1786,23 @@
       <c r="A21" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <f>B6+B9+B12+B16+B19</f>
         <v>1975000</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>C6+C9+C12+C16+C19</f>
         <v>2612670</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>D6+D9+D12+D16+D19</f>
         <v>3286760</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>E6+E9+E12+E16+E19</f>
         <v>3895050</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <f>F6+F9+F12+F16+F19</f>
         <v>4323000</v>
       </c>
@@ -1815,28 +1842,28 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="25" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1850,19 +1877,19 @@
       <c r="C4" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <v>1</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>95000</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>0.25</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <v>126017.5</v>
       </c>
     </row>
@@ -1876,19 +1903,19 @@
       <c r="C5" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>1</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>75000</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>0.25</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <v>99487.5</v>
       </c>
     </row>
@@ -1902,19 +1929,19 @@
       <c r="C6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>6</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>48000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>0.25</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <v>382032</v>
       </c>
     </row>
@@ -1928,19 +1955,19 @@
       <c r="C7" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <v>3</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>32000</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>0.2</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <v>122544</v>
       </c>
     </row>
@@ -1954,19 +1981,19 @@
       <c r="C8" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>1</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>52000</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>0.25</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <v>68978</v>
       </c>
     </row>
@@ -1980,19 +2007,19 @@
       <c r="C9" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>42000</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>0.25</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <v>55713</v>
       </c>
     </row>
@@ -2012,7 +2039,7 @@
       <c r="A12" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="33">
         <v>6</v>
       </c>
     </row>
@@ -2020,7 +2047,7 @@
       <c r="A13" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="33">
         <v>13</v>
       </c>
     </row>
@@ -2028,7 +2055,7 @@
       <c r="A14" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>648000</v>
       </c>
     </row>
@@ -2036,7 +2063,7 @@
       <c r="A15" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>157200</v>
       </c>
     </row>
@@ -2044,7 +2071,7 @@
       <c r="A16" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>49572</v>
       </c>
     </row>
@@ -2052,15 +2079,15 @@
       <c r="A17" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <v>854772</v>
       </c>
     </row>
@@ -2075,22 +2102,22 @@
       <c r="F20" s="8"/>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2098,19 +2125,19 @@
       <c r="A22" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <v>854772</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <v>854772</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <v>854772</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <v>854772</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <v>854772</v>
       </c>
     </row>
@@ -2118,23 +2145,23 @@
       <c r="A23" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="34">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="34">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="34">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="34">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="34">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
@@ -2143,20 +2170,20 @@
       <c r="A24" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="35">
         <f>Assumptions!B31</f>
         <v>1</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="35">
         <v>1</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="35">
         <v>1</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="35">
         <v>1</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="35">
         <v>1</v>
       </c>
     </row>
@@ -2164,23 +2191,23 @@
       <c r="A25" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="28">
         <f>B22*B23*B24</f>
         <v>854772</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="28">
         <f>C22*C23*C24</f>
         <v>854772</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>D22*D23*D24</f>
         <v>854772</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>E22*E23*E24</f>
         <v>854772</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="28">
         <f>F22*F23*F24</f>
         <v>854772</v>
       </c>
@@ -2211,22 +2238,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2234,23 +2261,23 @@
       <c r="A2" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>100</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>130</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>160</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>185</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>200</v>
       </c>
@@ -2269,23 +2296,23 @@
       <c r="A4" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>600*Assumptions!B22</f>
         <v>60000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>618*Assumptions!B23</f>
         <v>80340</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>637*Assumptions!B24</f>
         <v>101920</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>656*Assumptions!B25</f>
         <v>121360</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>675*Assumptions!B26</f>
         <v>135000</v>
       </c>
@@ -2294,23 +2321,23 @@
       <c r="A5" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUM(B4:B4)</f>
         <v>60000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>SUM(C4:C4)</f>
         <v>80340</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>SUM(D4:D4)</f>
         <v>101920</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>SUM(E4:E4)</f>
         <v>121360</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>SUM(F4:F4)</f>
         <v>135000</v>
       </c>
@@ -2329,23 +2356,23 @@
       <c r="A7" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>400*Assumptions!B22</f>
         <v>40000</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>412*Assumptions!B23</f>
         <v>53560</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>424*Assumptions!B24</f>
         <v>67840</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>437*Assumptions!B25</f>
         <v>80845</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>450*Assumptions!B26</f>
         <v>90000</v>
       </c>
@@ -2354,23 +2381,23 @@
       <c r="A8" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>SUM(B7:B7)</f>
         <v>40000</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>SUM(C7:C7)</f>
         <v>53560</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>SUM(D7:D7)</f>
         <v>67840</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>SUM(E7:E7)</f>
         <v>80845</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>SUM(F7:F7)</f>
         <v>90000</v>
       </c>
@@ -2389,23 +2416,23 @@
       <c r="A10" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>8500*12</f>
         <v>102000</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>8755*12</f>
         <v>105060</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>9018*12</f>
         <v>108216</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>9289*12</f>
         <v>111468</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>9567*12</f>
         <v>114804</v>
       </c>
@@ -2414,23 +2441,23 @@
       <c r="A11" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>1200*12</f>
         <v>14400</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>1236*12</f>
         <v>14832</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>1273*12</f>
         <v>15276</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>1311*12</f>
         <v>15732</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>1350*12</f>
         <v>16200</v>
       </c>
@@ -2439,19 +2466,19 @@
       <c r="A12" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>12000</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>12360</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <v>12731</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>13113</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <v>13506</v>
       </c>
     </row>
@@ -2459,19 +2486,19 @@
       <c r="A13" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <v>8000</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <v>8240</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <v>8487</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <v>8742</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <v>9004</v>
       </c>
     </row>
@@ -2479,23 +2506,23 @@
       <c r="A14" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>SUM(B10:B13)</f>
         <v>136400</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>SUM(C10:C13)</f>
         <v>140492</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>SUM(D10:D13)</f>
         <v>144710</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>SUM(E10:E13)</f>
         <v>149055</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>SUM(F10:F13)</f>
         <v>153514</v>
       </c>
@@ -2514,19 +2541,19 @@
       <c r="A16" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <v>15000</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <v>15450</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <v>15914</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <v>16391</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="27">
         <v>16883</v>
       </c>
     </row>
@@ -2534,19 +2561,19 @@
       <c r="A17" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <v>8000</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <v>8240</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <v>8487</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>8742</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <v>9004</v>
       </c>
     </row>
@@ -2554,19 +2581,19 @@
       <c r="A18" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <v>12000</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <v>12360</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <v>12731</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <v>13113</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <v>13506</v>
       </c>
     </row>
@@ -2574,23 +2601,23 @@
       <c r="A19" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="28">
         <f>SUM(B16:B18)</f>
         <v>35000</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>SUM(C16:C18)</f>
         <v>36050</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>SUM(D16:D18)</f>
         <v>37132</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>SUM(E16:E18)</f>
         <v>38246</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <f>SUM(F16:F18)</f>
         <v>39393</v>
       </c>
@@ -2599,23 +2626,23 @@
       <c r="A21" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <f>B5+B8+B14+B19</f>
         <v>271400</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>C5+C8+C14+C19</f>
         <v>310442</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>D5+D8+D14+D19</f>
         <v>351602</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>E5+E8+E14+E19</f>
         <v>389506</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <f>F5+F8+F14+F19</f>
         <v>417907</v>
       </c>
@@ -2643,22 +2670,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2676,19 +2703,19 @@
       <c r="A3" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <v>34064.39316600799</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <v>34064.39316600799</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <v>34064.39316600799</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <v>34064.39316600799</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <v>34064.39316600799</v>
       </c>
     </row>
@@ -2696,19 +2723,19 @@
       <c r="A4" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <v>25000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>10000</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <v>10000</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>5000</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <v>5000</v>
       </c>
     </row>
@@ -2716,23 +2743,23 @@
       <c r="A5" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUM(B3:B4)</f>
         <v>59064</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>SUM(C3:C4)</f>
         <v>44064</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>SUM(D3:D4)</f>
         <v>44064</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>SUM(E3:E4)</f>
         <v>39064</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>SUM(F3:F4)</f>
         <v>39064</v>
       </c>
@@ -2760,22 +2787,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2783,23 +2810,23 @@
       <c r="A2" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>'Revenue Schedule'!B21</f>
         <v>1975000</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <f>'Revenue Schedule'!C21</f>
         <v>2612670</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="27">
         <f>'Revenue Schedule'!D21</f>
         <v>3286760</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="27">
         <f>'Revenue Schedule'!E21</f>
         <v>3895050</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="27">
         <f>'Revenue Schedule'!F21</f>
         <v>4323000</v>
       </c>
@@ -2808,23 +2835,23 @@
       <c r="A3" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>'Staffing &amp; Personnel'!B25</f>
         <v>854772</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>'Staffing &amp; Personnel'!C25</f>
         <v>854772</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>'Staffing &amp; Personnel'!D25</f>
         <v>854772</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>'Staffing &amp; Personnel'!E25</f>
         <v>854772</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>'Staffing &amp; Personnel'!F25</f>
         <v>854772</v>
       </c>
@@ -2833,23 +2860,23 @@
       <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>'Operating Expenses'!B21</f>
         <v>271400</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>'Operating Expenses'!C21</f>
         <v>310442</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>'Operating Expenses'!D21</f>
         <v>351602</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>'Operating Expenses'!E21</f>
         <v>389506</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>'Operating Expenses'!F21</f>
         <v>417907</v>
       </c>
@@ -2858,23 +2885,23 @@
       <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>'Capital &amp; Debt'!B5</f>
         <v>59064</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>'Capital &amp; Debt'!C5</f>
         <v>44064</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>'Capital &amp; Debt'!D5</f>
         <v>44064</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>'Capital &amp; Debt'!E5</f>
         <v>39064</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>'Capital &amp; Debt'!F5</f>
         <v>39064</v>
       </c>
@@ -2883,23 +2910,23 @@
       <c r="A6" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>B3+B4+B5</f>
         <v>1185236</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>C3+C4+C5</f>
         <v>1209278</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>D3+D4+D5</f>
         <v>1250438</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>E3+E4+E5</f>
         <v>1283342</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>F3+F4+F5</f>
         <v>1311743</v>
       </c>
@@ -2908,23 +2935,23 @@
       <c r="A7" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>B2-B6</f>
         <v>789764</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C2-C6</f>
         <v>1403392</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>D2-D6</f>
         <v>2036322</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>E2-E6</f>
         <v>2611708</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>F2-F6</f>
         <v>3011257</v>
       </c>
@@ -2933,23 +2960,23 @@
       <c r="A8" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>B7</f>
         <v>789764</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>B8+C7</f>
         <v>2193156</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>C8+D7</f>
         <v>4229478</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>D8+E7</f>
         <v>6841186</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>E8+F7</f>
         <v>9852443</v>
       </c>
@@ -2958,23 +2985,23 @@
       <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="36">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>7.996017670742367</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="36">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>21.763293469326324</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="36">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>40.58876649621972</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="36">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>63.969099429458396</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="36">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>90.1314632515668</v>
       </c>
@@ -3002,17 +3029,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>151</v>
       </c>
     </row>
@@ -3030,7 +3057,7 @@
       <c r="A5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3038,7 +3065,7 @@
       <c r="A6" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="33" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3046,7 +3073,7 @@
       <c r="A7" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="33" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3054,7 +3081,7 @@
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="33" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3062,7 +3089,7 @@
       <c r="A9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="33" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3070,7 +3097,7 @@
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="33" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3078,7 +3105,7 @@
       <c r="A11" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="33" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3086,7 +3113,7 @@
       <c r="A12" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="33" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3101,22 +3128,22 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3124,23 +3151,23 @@
       <c r="A16" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>'Revenue Schedule'!B2</f>
         <v>100</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>'Revenue Schedule'!C2</f>
         <v>130</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>'Revenue Schedule'!D2</f>
         <v>160</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>'Revenue Schedule'!E2</f>
         <v>185</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>'Revenue Schedule'!F2</f>
         <v>200</v>
       </c>
@@ -3152,40 +3179,40 @@
       <c r="B17" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="39">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.3</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="39">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="39">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.15625</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="39">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.08108108108108109</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3193,23 +3220,23 @@
       <c r="A20" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>'Financial Model'!B2</f>
         <v>1975000</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>'Financial Model'!C2</f>
         <v>2612670</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>'Financial Model'!D2</f>
         <v>3286760</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>'Financial Model'!E2</f>
         <v>3895050</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>'Financial Model'!F2</f>
         <v>4323000</v>
       </c>
@@ -3218,23 +3245,23 @@
       <c r="A21" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>'Financial Model'!B3</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>'Financial Model'!C3</f>
         <v>854772</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>'Financial Model'!D3</f>
         <v>854772</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>'Financial Model'!E3</f>
         <v>854772</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>'Financial Model'!F3</f>
         <v>854772</v>
       </c>
@@ -3243,23 +3270,23 @@
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>'Financial Model'!B4</f>
         <v>271400</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>'Financial Model'!C4</f>
         <v>310442</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>'Financial Model'!D4</f>
         <v>351602</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>'Financial Model'!E4</f>
         <v>389506</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>'Financial Model'!F4</f>
         <v>417907</v>
       </c>
@@ -3268,48 +3295,48 @@
       <c r="A23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="28">
         <f>'Financial Model'!B6</f>
         <v>1185236</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>'Financial Model'!C6</f>
         <v>1209278</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>'Financial Model'!D6</f>
         <v>1250438</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>'Financial Model'!E6</f>
         <v>1283342</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="28">
         <f>'Financial Model'!F6</f>
         <v>1311743</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="38">
+      <c r="B24" s="40">
         <f>'Financial Model'!B7</f>
         <v>789764</v>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="40">
         <f>'Financial Model'!C7</f>
         <v>1403392</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="40">
         <f>'Financial Model'!D7</f>
         <v>2036322</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="40">
         <f>'Financial Model'!E7</f>
         <v>2611708</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="40">
         <f>'Financial Model'!F7</f>
         <v>3011257</v>
       </c>
@@ -3318,29 +3345,29 @@
       <c r="A25" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>'Financial Model'!B8</f>
         <v>789764</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>'Financial Model'!C8</f>
         <v>2193156</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>'Financial Model'!D8</f>
         <v>4229478</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <f>'Financial Model'!E8</f>
         <v>6841186</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <f>'Financial Model'!F8</f>
         <v>9852443</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="13">
@@ -3378,23 +3405,23 @@
       <c r="A29" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>19750</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>20097.46153846154</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="27">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>20542.25</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="27">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>21054.324324324323</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="27">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>21615</v>
       </c>
@@ -3403,23 +3430,23 @@
       <c r="A30" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="39">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.4327959493670886</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="39">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.3271641653940222</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="39">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.26006523141330673</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="39">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.21945084145261293</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="39">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.1977265787647467</v>
       </c>
@@ -3428,29 +3455,29 @@
       <c r="A31" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="39">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.13741772151898735</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="39">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.11882174174312102</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="39">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.10697525830909467</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="39">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.10000025673611379</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="39">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.0966705991209808</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="33" t="s">
         <v>160</v>
       </c>
       <c r="B32" s="12">
@@ -3488,19 +3515,19 @@
       <c r="A35" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="39">
         <v>0.5675057208237986</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="39">
         <v>0.5732777238345675</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="39">
         <v>0.5768052612509744</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="39">
         <v>0.5789280554886744</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="39">
         <v>0.5801743191959632</v>
       </c>
     </row>
@@ -3508,19 +3535,19 @@
       <c r="A36" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="39">
         <v>0.39816933638443935</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="39">
         <v>0.4025342174644695</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="39">
         <v>0.4053534765757952</v>
       </c>
-      <c r="E36" s="37">
+      <c r="E36" s="39">
         <v>0.4071812549774971</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="39">
         <v>0.4083573126485675</v>
       </c>
     </row>
@@ -3528,19 +3555,19 @@
       <c r="A37" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="39">
         <v>0.034324942791762014</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="39">
         <v>0.02418805870096303</v>
       </c>
-      <c r="D37" s="37">
+      <c r="D37" s="39">
         <v>0.01784126217323042</v>
       </c>
-      <c r="E37" s="37">
+      <c r="E37" s="39">
         <v>0.01389068953382846</v>
       </c>
-      <c r="F37" s="37">
+      <c r="F37" s="39">
         <v>0.01146836815546937</v>
       </c>
     </row>
@@ -3585,7 +3612,7 @@
       <c r="A4" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="41">
         <v>85</v>
       </c>
     </row>
@@ -3593,7 +3620,7 @@
       <c r="A5" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="32">
         <v>1200000</v>
       </c>
     </row>
@@ -3601,7 +3628,7 @@
       <c r="A6" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="32">
         <v>1150000</v>
       </c>
     </row>
@@ -3609,7 +3636,7 @@
       <c r="A7" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="32">
         <v>75000</v>
       </c>
     </row>
@@ -3617,7 +3644,7 @@
       <c r="A8" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <v>50000</v>
       </c>
     </row>
@@ -3625,7 +3652,7 @@
       <c r="A9" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="42">
         <v>0.8</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="171">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -111,6 +111,12 @@
     <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
     <t>SCHOOL INFORMATION</t>
   </si>
   <si>
@@ -232,9 +238,6 @@
   </si>
   <si>
     <t>5 Years</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Year 1</t>
@@ -561,7 +564,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -634,6 +637,12 @@
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -753,7 +762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -773,28 +782,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1154,222 +1165,230 @@
       </c>
       <c r="B1" s="18"/>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>27</v>
+      <c r="A5" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>29</v>
+      <c r="A6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>31</v>
+      <c r="A7" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>33</v>
+      <c r="A8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>35</v>
+      <c r="A9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="22">
         <v>2023</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="20">
+      <c r="A11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="22">
         <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="20">
+      <c r="A12" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="22">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>40</v>
+      <c r="A13" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>42</v>
+      <c r="A14" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>44</v>
+      <c r="A15" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>46</v>
+      <c r="A16" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>48</v>
+      <c r="A17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>50</v>
+      <c r="A18" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>52</v>
+      <c r="A19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="21">
+      <c r="A22" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="23">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="21">
+      <c r="A23" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="23">
         <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="21">
+      <c r="A24" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="23">
         <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="21">
+      <c r="A25" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="23">
         <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="21">
+      <c r="A26" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="23">
         <v>200</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="22">
+      <c r="A29" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="22">
+      <c r="A30" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="A31" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>64</v>
+      <c r="A32" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1398,53 +1417,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>70</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>100</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>130</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>160</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>185</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1453,83 +1472,83 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="29">
         <f>10500*Assumptions!B22</f>
         <v>1050000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>10815*Assumptions!B23</f>
         <v>1405950</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>11140*Assumptions!B24</f>
         <v>1782400</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>11474*Assumptions!B25</f>
         <v>2122690</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>11818*Assumptions!B26</f>
         <v>2363600</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="27">
+      <c r="A5" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="29">
         <f>350*Assumptions!B22</f>
         <v>35000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>350*Assumptions!B23</f>
         <v>45500</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>350*Assumptions!B24</f>
         <v>56000</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>350*Assumptions!B25</f>
         <v>64750</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>350*Assumptions!B26</f>
         <v>70000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="28">
+        <v>76</v>
+      </c>
+      <c r="B6" s="30">
         <f>SUM(B4:B5)</f>
         <v>1085000</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>SUM(C4:C5)</f>
         <v>1451450</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>SUM(D4:D5)</f>
         <v>1838400</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>SUM(E4:E5)</f>
         <v>2187440</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>SUM(F4:F5)</f>
         <v>2433600</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1538,58 +1557,58 @@
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="29">
         <f>--1050*Assumptions!B22</f>
         <v>-105000</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <f>--1082*Assumptions!B23</f>
         <v>-140660</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>--1114*Assumptions!B24</f>
         <v>-178240</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="29">
         <f>--1147*Assumptions!B25</f>
         <v>-212195</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <f>--1182*Assumptions!B26</f>
         <v>-236400</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="28">
+        <v>79</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
         <v>-105000</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="30">
         <f>SUM(C8:C8)</f>
         <v>-140660</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="30">
         <f>SUM(D8:D8)</f>
         <v>-178240</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="30">
         <f>SUM(E8:E8)</f>
         <v>-212195</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="30">
         <f>SUM(F8:F8)</f>
         <v>-236400</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1598,58 +1617,58 @@
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="29">
         <f>8700*Assumptions!B22</f>
         <v>870000</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <f>8961*Assumptions!B23</f>
         <v>1164930</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <f>9230*Assumptions!B24</f>
         <v>1476800</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <f>9507*Assumptions!B25</f>
         <v>1758795</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="29">
         <f>9792*Assumptions!B26</f>
         <v>1958400</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="28">
+        <v>82</v>
+      </c>
+      <c r="B12" s="30">
         <f>SUM(B11:B11)</f>
         <v>870000</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="30">
         <f>SUM(C11:C11)</f>
         <v>1164930</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="30">
         <f>SUM(D11:D11)</f>
         <v>1476800</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="30">
         <f>SUM(E11:E11)</f>
         <v>1758795</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="30">
         <f>SUM(F11:F11)</f>
         <v>1958400</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1658,73 +1677,73 @@
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="27">
+      <c r="A14" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="29">
         <v>50000</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="29">
         <v>40000</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="29">
         <v>30000</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="29">
         <v>20000</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="29">
         <v>10000</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="27">
+      <c r="A15" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="29">
         <v>25000</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="29">
         <v>30000</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="29">
         <v>35000</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="29">
         <v>40000</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="29">
         <v>45000</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="28" t="str">
+        <v>86</v>
+      </c>
+      <c r="B16" s="30" t="str">
         <f>SUM(B14:B15)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="28" t="str">
+      <c r="C16" s="30" t="str">
         <f>SUM(C14:C15)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="28" t="str">
+      <c r="D16" s="30" t="str">
         <f>SUM(D14:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="28" t="str">
+      <c r="E16" s="30" t="str">
         <f>SUM(E14:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="28" t="str">
+      <c r="F16" s="30" t="str">
         <f>SUM(F14:F15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1733,76 +1752,76 @@
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" s="27">
+      <c r="A18" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="29">
         <f>500*Assumptions!B22</f>
         <v>50000</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="29">
         <f>515*Assumptions!B23</f>
         <v>66950</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="29">
         <f>530*Assumptions!B24</f>
         <v>84800</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="29">
         <f>546*Assumptions!B25</f>
         <v>101010</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="29">
         <f>562*Assumptions!B26</f>
         <v>112400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="28">
+        <v>89</v>
+      </c>
+      <c r="B19" s="30">
         <f>SUM(B18:B18)</f>
         <v>50000</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="30">
         <f>SUM(C18:C18)</f>
         <v>66950</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="30">
         <f>SUM(D18:D18)</f>
         <v>84800</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="30">
         <f>SUM(E18:E18)</f>
         <v>101010</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="30">
         <f>SUM(F18:F18)</f>
         <v>112400</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="28">
+        <v>90</v>
+      </c>
+      <c r="B21" s="30">
         <f>B6+B9+B12+B16+B19</f>
         <v>1975000</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="30">
         <f>C6+C9+C12+C16+C19</f>
         <v>2612670</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="30">
         <f>D6+D9+D12+D16+D19</f>
         <v>3286760</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="30">
         <f>E6+E9+E12+E16+E19</f>
         <v>3895050</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="30">
         <f>F6+F9+F12+F16+F19</f>
         <v>4323000</v>
       </c>
@@ -1831,7 +1850,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1842,51 +1861,51 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="D3" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="F3" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="27" t="s">
         <v>98</v>
       </c>
+      <c r="H3" s="27" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="29">
+      <c r="C4" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="25">
         <v>1</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>95000</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="24">
         <v>0.25</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="24">
         <v>0.0765</v>
       </c>
       <c r="H4" s="32">
@@ -1894,25 +1913,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>1</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>75000</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="24">
         <v>0.25</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="24">
         <v>0.0765</v>
       </c>
       <c r="H5" s="32">
@@ -1920,25 +1939,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="A6" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="29">
+      <c r="B6" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="25">
         <v>6</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>48000</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="24">
         <v>0.25</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="24">
         <v>0.0765</v>
       </c>
       <c r="H6" s="32">
@@ -1946,25 +1965,25 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="29">
+      <c r="C7" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="25">
         <v>3</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>32000</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="24">
         <v>0.2</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="24">
         <v>0.0765</v>
       </c>
       <c r="H7" s="32">
@@ -1972,25 +1991,25 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="19" t="s">
+      <c r="A8" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="29">
+      <c r="B8" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>52000</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="24">
         <v>0.25</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="24">
         <v>0.0765</v>
       </c>
       <c r="H8" s="32">
@@ -1998,25 +2017,25 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="B9" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="25">
         <v>1</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>42000</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="24">
         <v>0.25</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="24">
         <v>0.0765</v>
       </c>
       <c r="H9" s="32">
@@ -2025,7 +2044,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2036,64 +2055,64 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>111</v>
+      <c r="A12" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="B12" s="33">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>112</v>
+      <c r="A13" s="21" t="s">
+        <v>113</v>
       </c>
       <c r="B13" s="33">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="30">
+      <c r="A14" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="34">
         <v>648000</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="30">
+      <c r="A15" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="34">
         <v>157200</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="30">
+      <c r="A16" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="34">
         <v>49572</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="30">
+      <c r="A17" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="32">
+        <v>118</v>
+      </c>
+      <c r="B18" s="35">
         <v>854772</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2102,112 +2121,112 @@
       <c r="F20" s="8"/>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="25" t="s">
+      <c r="A21" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="C21" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="D21" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="E21" s="27" t="s">
         <v>70</v>
       </c>
+      <c r="F21" s="27" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" s="27">
+      <c r="A22" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="29">
         <v>854772</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="29">
         <v>854772</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="29">
         <v>854772</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="29">
         <v>854772</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="29">
         <v>854772</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="34">
+      <c r="A23" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="36">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="36">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="36">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="36">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="36">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B24" s="35">
+      <c r="A24" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="37">
         <f>Assumptions!B31</f>
         <v>1</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="37">
         <v>1</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="37">
         <v>1</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="37">
         <v>1</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="28">
+        <v>123</v>
+      </c>
+      <c r="B25" s="30">
         <f>B22*B23*B24</f>
         <v>854772</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="30">
         <f>C22*C23*C24</f>
         <v>854772</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="30">
         <f>D22*D23*D24</f>
         <v>854772</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="30">
         <f>E22*E23*E24</f>
         <v>854772</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="30">
         <f>F22*F23*F24</f>
         <v>854772</v>
       </c>
@@ -2238,53 +2257,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>70</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>100</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>130</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>160</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>185</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2293,58 +2312,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="29">
         <f>600*Assumptions!B22</f>
         <v>60000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>618*Assumptions!B23</f>
         <v>80340</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>637*Assumptions!B24</f>
         <v>101920</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>656*Assumptions!B25</f>
         <v>121360</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>675*Assumptions!B26</f>
         <v>135000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="28">
+        <v>126</v>
+      </c>
+      <c r="B5" s="30">
         <f>SUM(B4:B4)</f>
         <v>60000</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="30">
         <f>SUM(C4:C4)</f>
         <v>80340</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="30">
         <f>SUM(D4:D4)</f>
         <v>101920</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>SUM(E4:E4)</f>
         <v>121360</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="30">
         <f>SUM(F4:F4)</f>
         <v>135000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2353,58 +2372,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B7" s="27">
+      <c r="A7" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="29">
         <f>400*Assumptions!B22</f>
         <v>40000</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="29">
         <f>412*Assumptions!B23</f>
         <v>53560</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <f>424*Assumptions!B24</f>
         <v>67840</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="29">
         <f>437*Assumptions!B25</f>
         <v>80845</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="29">
         <f>450*Assumptions!B26</f>
         <v>90000</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="28">
+        <v>129</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B7:B7)</f>
         <v>40000</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="30">
         <f>SUM(C7:C7)</f>
         <v>53560</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="30">
         <f>SUM(D7:D7)</f>
         <v>67840</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="30">
         <f>SUM(E7:E7)</f>
         <v>80845</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="30">
         <f>SUM(F7:F7)</f>
         <v>90000</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2413,123 +2432,123 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="29">
         <f>8500*12</f>
         <v>102000</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <f>8755*12</f>
         <v>105060</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <f>9018*12</f>
         <v>108216</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <f>9289*12</f>
         <v>111468</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <f>9567*12</f>
         <v>114804</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="29">
         <f>1200*12</f>
         <v>14400</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <f>1236*12</f>
         <v>14832</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <f>1273*12</f>
         <v>15276</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <f>1311*12</f>
         <v>15732</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="29">
         <f>1350*12</f>
         <v>16200</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="27">
+      <c r="A12" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="29">
         <v>12000</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="29">
         <v>12360</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <v>12731</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="29">
         <v>13113</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <v>13506</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="27">
+      <c r="A13" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="29">
         <v>8000</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="29">
         <v>8240</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <v>8487</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="29">
         <v>8742</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="29">
         <v>9004</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B14" s="28">
+        <v>135</v>
+      </c>
+      <c r="B14" s="30">
         <f>SUM(B10:B13)</f>
         <v>136400</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="30">
         <f>SUM(C10:C13)</f>
         <v>140492</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="30">
         <f>SUM(D10:D13)</f>
         <v>144710</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="30">
         <f>SUM(E10:E13)</f>
         <v>149055</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="30">
         <f>SUM(F10:F13)</f>
         <v>153514</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2538,111 +2557,111 @@
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="27">
+      <c r="A16" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="29">
         <v>15000</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="29">
         <v>15450</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="29">
         <v>15914</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="29">
         <v>16391</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="29">
         <v>16883</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="27">
+      <c r="A17" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="29">
         <v>8000</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="29">
         <v>8240</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="29">
         <v>8487</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="29">
         <v>8742</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="29">
         <v>9004</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B18" s="27">
+      <c r="A18" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="29">
         <v>12000</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="29">
         <v>12360</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="29">
         <v>12731</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="29">
         <v>13113</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="29">
         <v>13506</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="28">
+        <v>140</v>
+      </c>
+      <c r="B19" s="30">
         <f>SUM(B16:B18)</f>
         <v>35000</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="30">
         <f>SUM(C16:C18)</f>
         <v>36050</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="30">
         <f>SUM(D16:D18)</f>
         <v>37132</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="30">
         <f>SUM(E16:E18)</f>
         <v>38246</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="30">
         <f>SUM(F16:F18)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21" s="28">
+        <v>141</v>
+      </c>
+      <c r="B21" s="30">
         <f>B5+B8+B14+B19</f>
         <v>271400</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="30">
         <f>C5+C8+C14+C19</f>
         <v>310442</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="30">
         <f>D5+D8+D14+D19</f>
         <v>351602</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="30">
         <f>E5+E8+E14+E19</f>
         <v>389506</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="30">
         <f>F5+F8+F14+F19</f>
         <v>417907</v>
       </c>
@@ -2670,28 +2689,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>70</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2700,66 +2719,66 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="29">
         <v>34064.39316600799</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <v>34064.39316600799</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <v>34064.39316600799</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <v>34064.39316600799</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <v>34064.39316600799</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="29">
         <v>25000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <v>10000</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <v>10000</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <v>5000</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <v>5000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="28">
+        <v>145</v>
+      </c>
+      <c r="B5" s="30">
         <f>SUM(B3:B4)</f>
         <v>59064</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="30">
         <f>SUM(C3:C4)</f>
         <v>44064</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="30">
         <f>SUM(D3:D4)</f>
         <v>44064</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>SUM(E3:E4)</f>
         <v>39064</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="30">
         <f>SUM(F3:F4)</f>
         <v>39064</v>
       </c>
@@ -2787,221 +2806,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="B1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>70</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="29">
         <f>'Revenue Schedule'!B21</f>
         <v>1975000</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="29">
         <f>'Revenue Schedule'!C21</f>
         <v>2612670</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="29">
         <f>'Revenue Schedule'!D21</f>
         <v>3286760</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="29">
         <f>'Revenue Schedule'!E21</f>
         <v>3895050</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="29">
         <f>'Revenue Schedule'!F21</f>
         <v>4323000</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="29">
         <f>'Staffing &amp; Personnel'!B25</f>
         <v>854772</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <f>'Staffing &amp; Personnel'!C25</f>
         <v>854772</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <f>'Staffing &amp; Personnel'!D25</f>
         <v>854772</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <f>'Staffing &amp; Personnel'!E25</f>
         <v>854772</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <f>'Staffing &amp; Personnel'!F25</f>
         <v>854772</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="29">
         <f>'Operating Expenses'!B21</f>
         <v>271400</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>'Operating Expenses'!C21</f>
         <v>310442</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>'Operating Expenses'!D21</f>
         <v>351602</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>'Operating Expenses'!E21</f>
         <v>389506</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>'Operating Expenses'!F21</f>
         <v>417907</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="29">
         <f>'Capital &amp; Debt'!B5</f>
         <v>59064</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>'Capital &amp; Debt'!C5</f>
         <v>44064</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>'Capital &amp; Debt'!D5</f>
         <v>44064</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>'Capital &amp; Debt'!E5</f>
         <v>39064</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>'Capital &amp; Debt'!F5</f>
         <v>39064</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="28">
+        <v>148</v>
+      </c>
+      <c r="B6" s="30">
         <f>B3+B4+B5</f>
         <v>1185236</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>C3+C4+C5</f>
         <v>1209278</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>D3+D4+D5</f>
         <v>1250438</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>E3+E4+E5</f>
         <v>1283342</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>F3+F4+F5</f>
         <v>1311743</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="28">
+        <v>149</v>
+      </c>
+      <c r="B7" s="30">
         <f>B2-B6</f>
         <v>789764</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="30">
         <f>C2-C6</f>
         <v>1403392</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="30">
         <f>D2-D6</f>
         <v>2036322</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>E2-E6</f>
         <v>2611708</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="30">
         <f>F2-F6</f>
         <v>3011257</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="29">
         <f>B7</f>
         <v>789764</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <f>B8+C7</f>
         <v>2193156</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>C8+D7</f>
         <v>4229478</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="29">
         <f>D8+E7</f>
         <v>6841186</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <f>E8+F7</f>
         <v>9852443</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="38">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>7.996017670742367</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="38">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>21.763293469326324</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="38">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>40.58876649621972</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="38">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>63.969099429458396</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="38">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>90.1314632515668</v>
       </c>
@@ -3029,23 +3048,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="A1" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>151</v>
+      <c r="A2" s="40" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -3054,72 +3073,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>25</v>
+      <c r="A5" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B10" s="33" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>27</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>39</v>
+      <c r="A11" s="21" t="s">
+        <v>41</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>38</v>
-      </c>
       <c r="B12" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3128,240 +3147,240 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="25" t="s">
+      <c r="A15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="D15" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="E15" s="27" t="s">
         <v>70</v>
       </c>
+      <c r="F15" s="27" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="26">
+      <c r="A16" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="28">
         <f>'Revenue Schedule'!B2</f>
         <v>100</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="28">
         <f>'Revenue Schedule'!C2</f>
         <v>130</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="28">
         <f>'Revenue Schedule'!D2</f>
         <v>160</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="28">
         <f>'Revenue Schedule'!E2</f>
         <v>185</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="28">
         <f>'Revenue Schedule'!F2</f>
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>154</v>
+      <c r="A17" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="39">
+        <v>156</v>
+      </c>
+      <c r="C17" s="41">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.3</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="41">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="41">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.15625</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="41">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.08108108108108109</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="25" t="s">
+      <c r="A19" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="D19" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="E19" s="27" t="s">
         <v>70</v>
       </c>
+      <c r="F19" s="27" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="A20" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="29">
         <f>'Financial Model'!B2</f>
         <v>1975000</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="29">
         <f>'Financial Model'!C2</f>
         <v>2612670</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="29">
         <f>'Financial Model'!D2</f>
         <v>3286760</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="29">
         <f>'Financial Model'!E2</f>
         <v>3895050</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="29">
         <f>'Financial Model'!F2</f>
         <v>4323000</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="27">
+      <c r="A21" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="29">
         <f>'Financial Model'!B3</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="29">
         <f>'Financial Model'!C3</f>
         <v>854772</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="29">
         <f>'Financial Model'!D3</f>
         <v>854772</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="29">
         <f>'Financial Model'!E3</f>
         <v>854772</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="29">
         <f>'Financial Model'!F3</f>
         <v>854772</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="29">
         <f>'Financial Model'!B4</f>
         <v>271400</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="29">
         <f>'Financial Model'!C4</f>
         <v>310442</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="29">
         <f>'Financial Model'!D4</f>
         <v>351602</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="29">
         <f>'Financial Model'!E4</f>
         <v>389506</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="29">
         <f>'Financial Model'!F4</f>
         <v>417907</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B23" s="28">
+        <v>148</v>
+      </c>
+      <c r="B23" s="30">
         <f>'Financial Model'!B6</f>
         <v>1185236</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="30">
         <f>'Financial Model'!C6</f>
         <v>1209278</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="30">
         <f>'Financial Model'!D6</f>
         <v>1250438</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="30">
         <f>'Financial Model'!E6</f>
         <v>1283342</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="30">
         <f>'Financial Model'!F6</f>
         <v>1311743</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="40">
+        <v>149</v>
+      </c>
+      <c r="B24" s="42">
         <f>'Financial Model'!B7</f>
         <v>789764</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="42">
         <f>'Financial Model'!C7</f>
         <v>1403392</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="42">
         <f>'Financial Model'!D7</f>
         <v>2036322</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="42">
         <f>'Financial Model'!E7</f>
         <v>2611708</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="42">
         <f>'Financial Model'!F7</f>
         <v>3011257</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="A25" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="29">
         <f>'Financial Model'!B8</f>
         <v>789764</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="29">
         <f>'Financial Model'!C8</f>
         <v>2193156</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="29">
         <f>'Financial Model'!D8</f>
         <v>4229478</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="29">
         <f>'Financial Model'!E8</f>
         <v>6841186</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="29">
         <f>'Financial Model'!F8</f>
         <v>9852443</v>
       </c>
@@ -3393,7 +3412,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3402,83 +3421,83 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="27">
+      <c r="A29" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="29">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>19750</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="29">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>20097.46153846154</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="29">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>20542.25</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="29">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>21054.324324324323</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="29">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>21615</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B30" s="39">
+      <c r="A30" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="41">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.4327959493670886</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="41">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.3271641653940222</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="41">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.26006523141330673</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="41">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.21945084145261293</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="41">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.1977265787647467</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B31" s="39">
+      <c r="A31" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="41">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.13741772151898735</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="41">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.11882174174312102</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="41">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.10697525830909467</v>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="41">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.10000025673611379</v>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="41">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.0966705991209808</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
@@ -3503,7 +3522,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3512,62 +3531,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="39">
+      <c r="A35" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="41">
         <v>0.5675057208237986</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="41">
         <v>0.5732777238345675</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="41">
         <v>0.5768052612509744</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="41">
         <v>0.5789280554886744</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="41">
         <v>0.5801743191959632</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" s="39">
+      <c r="A36" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="41">
         <v>0.39816933638443935</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="41">
         <v>0.4025342174644695</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="41">
         <v>0.4053534765757952</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="41">
         <v>0.4071812549774971</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="41">
         <v>0.4083573126485675</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="39">
+      <c r="A37" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="41">
         <v>0.034324942791762014</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="41">
         <v>0.02418805870096303</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="41">
         <v>0.01784126217323042</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="41">
         <v>0.01389068953382846</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="41">
         <v>0.01146836815546937</v>
       </c>
     </row>
@@ -3604,55 +3623,55 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="41">
+      <c r="A4" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="43">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="32">
+      <c r="A5" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="35">
         <v>1200000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="32">
+      <c r="A6" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="35">
         <v>1150000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="32">
+      <c r="A7" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="35">
         <v>75000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" s="32">
+      <c r="A8" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="35">
         <v>50000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B9" s="42">
+      <c r="A9" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="44">
         <v>0.8</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -15,7 +15,7 @@
     <sheet sheetId="8" name="Prior-Year Snapshot" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$B32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="172">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -674,7 +677,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -698,11 +701,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -744,6 +752,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -762,7 +779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -784,13 +801,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -807,7 +825,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -1152,7 +1170,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1165,230 +1183,236 @@
       </c>
       <c r="B1" s="18"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>25</v>
       </c>
+      <c r="D2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="A5" s="22" t="s">
         <v>29</v>
       </c>
+      <c r="B5" s="23" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="22" t="s">
         <v>31</v>
       </c>
+      <c r="B6" s="23" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="22" t="s">
         <v>33</v>
       </c>
+      <c r="B7" s="23" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="22" t="s">
         <v>35</v>
       </c>
+      <c r="B8" s="23" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="22" t="s">
         <v>37</v>
       </c>
+      <c r="B9" s="23" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="A10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="23">
         <v>2023</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="23">
         <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="22">
+      <c r="A12" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="23">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="22" t="s">
         <v>42</v>
       </c>
+      <c r="B13" s="23" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="22" t="s">
+      <c r="A14" s="22" t="s">
         <v>44</v>
       </c>
+      <c r="B14" s="23" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="22" t="s">
         <v>46</v>
       </c>
+      <c r="B15" s="23" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="22" t="s">
         <v>48</v>
       </c>
+      <c r="B16" s="23" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="22" t="s">
         <v>50</v>
       </c>
+      <c r="B17" s="23" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="22" t="s">
         <v>52</v>
       </c>
+      <c r="B18" s="23" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="22" t="s">
         <v>54</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="23">
+      <c r="A22" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="24">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="23">
+      <c r="A23" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="24">
         <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="23">
+      <c r="A24" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="24">
         <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="23">
+      <c r="A25" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="24">
         <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="23">
+      <c r="A26" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="24">
         <v>200</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="24">
+      <c r="A29" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="24">
+      <c r="A30" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="25">
+      <c r="A31" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="22" t="s">
         <v>66</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1417,53 +1441,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>71</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>100</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>130</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>160</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>185</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1472,83 +1496,83 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="30">
         <f>10500*Assumptions!B22</f>
         <v>1050000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>10815*Assumptions!B23</f>
         <v>1405950</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>11140*Assumptions!B24</f>
         <v>1782400</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>11474*Assumptions!B25</f>
         <v>2122690</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>11818*Assumptions!B26</f>
         <v>2363600</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="30">
         <f>350*Assumptions!B22</f>
         <v>35000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>350*Assumptions!B23</f>
         <v>45500</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>350*Assumptions!B24</f>
         <v>56000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>350*Assumptions!B25</f>
         <v>64750</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>350*Assumptions!B26</f>
         <v>70000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="30">
+        <v>77</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B4:B5)</f>
         <v>1085000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>SUM(C4:C5)</f>
         <v>1451450</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>SUM(D4:D5)</f>
         <v>1838400</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>SUM(E4:E5)</f>
         <v>2187440</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>SUM(F4:F5)</f>
         <v>2433600</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1557,58 +1581,58 @@
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="29">
+      <c r="A8" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="30">
         <f>--1050*Assumptions!B22</f>
         <v>-105000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>--1082*Assumptions!B23</f>
         <v>-140660</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>--1114*Assumptions!B24</f>
         <v>-178240</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>--1147*Assumptions!B25</f>
         <v>-212195</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>--1182*Assumptions!B26</f>
         <v>-236400</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="30">
+        <v>80</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>-105000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>-140660</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>-178240</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>-212195</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>-236400</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1617,58 +1641,58 @@
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="30">
         <f>8700*Assumptions!B22</f>
         <v>870000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>8961*Assumptions!B23</f>
         <v>1164930</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>9230*Assumptions!B24</f>
         <v>1476800</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>9507*Assumptions!B25</f>
         <v>1758795</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>9792*Assumptions!B26</f>
         <v>1958400</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="30">
+        <v>83</v>
+      </c>
+      <c r="B12" s="31">
         <f>SUM(B11:B11)</f>
         <v>870000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>SUM(C11:C11)</f>
         <v>1164930</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>SUM(D11:D11)</f>
         <v>1476800</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>SUM(E11:E11)</f>
         <v>1758795</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>SUM(F11:F11)</f>
         <v>1958400</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1677,73 +1701,73 @@
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="29">
+      <c r="A14" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="30">
         <v>50000</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>40000</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>30000</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>20000</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>10000</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="A15" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="30">
         <v>25000</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>30000</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>35000</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>40000</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>45000</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="30" t="str">
+        <v>87</v>
+      </c>
+      <c r="B16" s="31" t="str">
         <f>SUM(B14:B15)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="30" t="str">
+      <c r="C16" s="31" t="str">
         <f>SUM(C14:C15)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="30" t="str">
+      <c r="D16" s="31" t="str">
         <f>SUM(D14:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="30" t="str">
+      <c r="E16" s="31" t="str">
         <f>SUM(E14:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="30" t="str">
+      <c r="F16" s="31" t="str">
         <f>SUM(F14:F15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1752,76 +1776,76 @@
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="A18" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="30">
         <f>500*Assumptions!B22</f>
         <v>50000</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>515*Assumptions!B23</f>
         <v>66950</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>530*Assumptions!B24</f>
         <v>84800</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>546*Assumptions!B25</f>
         <v>101010</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>562*Assumptions!B26</f>
         <v>112400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="30">
+        <v>90</v>
+      </c>
+      <c r="B19" s="31">
         <f>SUM(B18:B18)</f>
         <v>50000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>SUM(C18:C18)</f>
         <v>66950</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>SUM(D18:D18)</f>
         <v>84800</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>SUM(E18:E18)</f>
         <v>101010</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>SUM(F18:F18)</f>
         <v>112400</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="30">
+        <v>91</v>
+      </c>
+      <c r="B21" s="31">
         <f>B6+B9+B12+B16+B19</f>
         <v>1975000</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>C6+C9+C12+C16+C19</f>
         <v>2612670</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>D6+D9+D12+D16+D19</f>
         <v>3286760</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <f>E6+E9+E12+E16+E19</f>
         <v>3895050</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <f>F6+F9+F12+F16+F19</f>
         <v>4323000</v>
       </c>
@@ -1850,7 +1874,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1861,190 +1885,190 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="E3" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="G3" s="28" t="s">
         <v>99</v>
       </c>
+      <c r="H3" s="28" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="25">
+      <c r="C4" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="26">
         <v>1</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>95000</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="25">
         <v>0.25</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="33">
         <v>126017.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>1</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>75000</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>0.25</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="33">
         <v>99487.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="B6" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="26">
         <v>6</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <v>48000</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>0.25</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="33">
         <v>382032</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="25">
+      <c r="C7" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="26">
         <v>3</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <v>32000</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>0.2</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="33">
         <v>122544</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="B8" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <v>52000</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>0.25</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="33">
         <v>68978</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="25">
+      <c r="B9" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="26">
         <v>1</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <v>42000</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>0.25</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <v>55713</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2055,64 +2079,64 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="33">
+      <c r="A12" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="34">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="33">
+      <c r="A13" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="34">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="34">
+      <c r="A14" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="35">
         <v>648000</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="34">
+      <c r="A15" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="35">
         <v>157200</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="34">
+      <c r="A16" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="35">
         <v>49572</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="34">
+      <c r="A17" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="35">
+      <c r="A18" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="36">
         <v>854772</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2121,112 +2145,112 @@
       <c r="F20" s="8"/>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="27" t="s">
+      <c r="B21" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="C21" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="D21" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>71</v>
       </c>
+      <c r="F21" s="28" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="30">
         <v>854772</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>854772</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>854772</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>854772</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>854772</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B23" s="36">
+      <c r="A23" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="37">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="37">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="37">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="37">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="37">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="37">
+      <c r="A24" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="38">
         <f>Assumptions!B31</f>
         <v>1</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="38">
         <v>1</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="38">
         <v>1</v>
       </c>
-      <c r="E24" s="37">
+      <c r="E24" s="38">
         <v>1</v>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="38">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B25" s="30">
+        <v>124</v>
+      </c>
+      <c r="B25" s="31">
         <f>B22*B23*B24</f>
         <v>854772</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <f>C22*C23*C24</f>
         <v>854772</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <f>D22*D23*D24</f>
         <v>854772</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <f>E22*E23*E24</f>
         <v>854772</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <f>F22*F23*F24</f>
         <v>854772</v>
       </c>
@@ -2257,53 +2281,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>71</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>100</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>130</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>160</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>185</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2312,58 +2336,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="30">
         <f>600*Assumptions!B22</f>
         <v>60000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>618*Assumptions!B23</f>
         <v>80340</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>637*Assumptions!B24</f>
         <v>101920</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>656*Assumptions!B25</f>
         <v>121360</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>675*Assumptions!B26</f>
         <v>135000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="30">
+        <v>127</v>
+      </c>
+      <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
         <v>60000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUM(C4:C4)</f>
         <v>80340</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUM(D4:D4)</f>
         <v>101920</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUM(E4:E4)</f>
         <v>121360</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>SUM(F4:F4)</f>
         <v>135000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2372,58 +2396,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B7" s="29">
+      <c r="A7" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="30">
         <f>400*Assumptions!B22</f>
         <v>40000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>412*Assumptions!B23</f>
         <v>53560</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>424*Assumptions!B24</f>
         <v>67840</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>437*Assumptions!B25</f>
         <v>80845</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>450*Assumptions!B26</f>
         <v>90000</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="30">
+        <v>130</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
         <v>40000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C7:C7)</f>
         <v>53560</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D7:D7)</f>
         <v>67840</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E7:E7)</f>
         <v>80845</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F7:F7)</f>
         <v>90000</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2432,123 +2456,123 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B10" s="29">
+      <c r="A10" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="30">
         <f>8500*12</f>
         <v>102000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>8755*12</f>
         <v>105060</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>9018*12</f>
         <v>108216</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>9289*12</f>
         <v>111468</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>9567*12</f>
         <v>114804</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="30">
         <f>1200*12</f>
         <v>14400</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>1236*12</f>
         <v>14832</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>1273*12</f>
         <v>15276</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>1311*12</f>
         <v>15732</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>1350*12</f>
         <v>16200</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B12" s="29">
+      <c r="A12" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="30">
         <v>12000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>12360</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>12731</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>13113</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="B13" s="29">
+      <c r="A13" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="30">
         <v>8000</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>8240</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>8487</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>8742</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>9004</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B14" s="30">
+        <v>136</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B10:B13)</f>
         <v>136400</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C10:C13)</f>
         <v>140492</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D10:D13)</f>
         <v>144710</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E10:E13)</f>
         <v>149055</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F10:F13)</f>
         <v>153514</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2557,111 +2581,111 @@
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B16" s="29">
+      <c r="A16" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="30">
         <v>15000</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>15450</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>15914</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>16391</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>16883</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="29">
+      <c r="A17" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" s="30">
         <v>8000</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>8240</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>8487</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>8742</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>9004</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="A18" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="30">
         <v>12000</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>12360</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>12731</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>13113</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="30">
+        <v>141</v>
+      </c>
+      <c r="B19" s="31">
         <f>SUM(B16:B18)</f>
         <v>35000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>SUM(C16:C18)</f>
         <v>36050</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>SUM(D16:D18)</f>
         <v>37132</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>SUM(E16:E18)</f>
         <v>38246</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>SUM(F16:F18)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" s="30">
+        <v>142</v>
+      </c>
+      <c r="B21" s="31">
         <f>B5+B8+B14+B19</f>
         <v>271400</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>C5+C8+C14+C19</f>
         <v>310442</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>D5+D8+D14+D19</f>
         <v>351602</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <f>E5+E8+E14+E19</f>
         <v>389506</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <f>F5+F8+F14+F19</f>
         <v>417907</v>
       </c>
@@ -2689,28 +2713,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>71</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2719,66 +2743,66 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="30">
         <v>34064.39316600799</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>34064.39316600799</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <v>34064.39316600799</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <v>34064.39316600799</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <v>34064.39316600799</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="30">
         <v>25000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <v>10000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>10000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>5000</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>5000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="30">
+        <v>146</v>
+      </c>
+      <c r="B5" s="31">
         <f>SUM(B3:B4)</f>
         <v>59064</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUM(C3:C4)</f>
         <v>44064</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUM(D3:D4)</f>
         <v>44064</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUM(E3:E4)</f>
         <v>39064</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>SUM(F3:F4)</f>
         <v>39064</v>
       </c>
@@ -2806,221 +2830,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>71</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="29">
+      <c r="A2" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="30">
         <f>'Revenue Schedule'!B21</f>
         <v>1975000</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="30">
         <f>'Revenue Schedule'!C21</f>
         <v>2612670</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="30">
         <f>'Revenue Schedule'!D21</f>
         <v>3286760</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="30">
         <f>'Revenue Schedule'!E21</f>
         <v>3895050</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="30">
         <f>'Revenue Schedule'!F21</f>
         <v>4323000</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B25</f>
         <v>854772</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <f>'Staffing &amp; Personnel'!C25</f>
         <v>854772</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <f>'Staffing &amp; Personnel'!D25</f>
         <v>854772</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <f>'Staffing &amp; Personnel'!E25</f>
         <v>854772</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <f>'Staffing &amp; Personnel'!F25</f>
         <v>854772</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <f>'Operating Expenses'!B21</f>
         <v>271400</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>'Operating Expenses'!C21</f>
         <v>310442</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>'Operating Expenses'!D21</f>
         <v>351602</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>'Operating Expenses'!E21</f>
         <v>389506</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>'Operating Expenses'!F21</f>
         <v>417907</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <f>'Capital &amp; Debt'!B5</f>
         <v>59064</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>'Capital &amp; Debt'!C5</f>
         <v>44064</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>'Capital &amp; Debt'!D5</f>
         <v>44064</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>'Capital &amp; Debt'!E5</f>
         <v>39064</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>'Capital &amp; Debt'!F5</f>
         <v>39064</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="30">
+        <v>149</v>
+      </c>
+      <c r="B6" s="31">
         <f>B3+B4+B5</f>
         <v>1185236</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>C3+C4+C5</f>
         <v>1209278</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>D3+D4+D5</f>
         <v>1250438</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>E3+E4+E5</f>
         <v>1283342</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>F3+F4+F5</f>
         <v>1311743</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="30">
+        <v>150</v>
+      </c>
+      <c r="B7" s="31">
         <f>B2-B6</f>
         <v>789764</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>C2-C6</f>
         <v>1403392</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>D2-D6</f>
         <v>2036322</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>E2-E6</f>
         <v>2611708</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>F2-F6</f>
         <v>3011257</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="29">
+      <c r="A8" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="30">
         <f>B7</f>
         <v>789764</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>B8+C7</f>
         <v>2193156</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>C8+D7</f>
         <v>4229478</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>D8+E7</f>
         <v>6841186</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>E8+F7</f>
         <v>9852443</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="39">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>7.996017670742367</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>21.763293469326324</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="39">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>40.58876649621972</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="39">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>63.969099429458396</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>90.1314632515668</v>
       </c>
@@ -3048,23 +3072,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="A1" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>152</v>
+      <c r="A2" s="41" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -3073,72 +3097,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>153</v>
+      <c r="B12" s="34" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3147,246 +3171,246 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="C15" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="E15" s="28" t="s">
         <v>71</v>
       </c>
+      <c r="F15" s="28" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="28">
+      <c r="A16" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>100</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>130</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>160</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>185</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>155</v>
+      <c r="A17" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" s="41">
+        <v>157</v>
+      </c>
+      <c r="C17" s="42">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.3</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.15625</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="42">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.08108108108108109</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="C19" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="D19" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="E19" s="28" t="s">
         <v>71</v>
       </c>
+      <c r="F19" s="28" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="30">
         <f>'Financial Model'!B2</f>
         <v>1975000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>'Financial Model'!C2</f>
         <v>2612670</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>'Financial Model'!D2</f>
         <v>3286760</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>'Financial Model'!E2</f>
         <v>3895050</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>'Financial Model'!F2</f>
         <v>4323000</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="30">
         <f>'Financial Model'!B3</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>'Financial Model'!C3</f>
         <v>854772</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>'Financial Model'!D3</f>
         <v>854772</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>'Financial Model'!E3</f>
         <v>854772</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>'Financial Model'!F3</f>
         <v>854772</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <f>'Financial Model'!B4</f>
         <v>271400</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>'Financial Model'!C4</f>
         <v>310442</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>'Financial Model'!D4</f>
         <v>351602</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>'Financial Model'!E4</f>
         <v>389506</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>'Financial Model'!F4</f>
         <v>417907</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B23" s="30">
+        <v>149</v>
+      </c>
+      <c r="B23" s="31">
         <f>'Financial Model'!B6</f>
         <v>1185236</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>'Financial Model'!C6</f>
         <v>1209278</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>'Financial Model'!D6</f>
         <v>1250438</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>'Financial Model'!E6</f>
         <v>1283342</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <f>'Financial Model'!F6</f>
         <v>1311743</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="42">
+      <c r="A24" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="43">
         <f>'Financial Model'!B7</f>
         <v>789764</v>
       </c>
-      <c r="C24" s="42">
+      <c r="C24" s="43">
         <f>'Financial Model'!C7</f>
         <v>1403392</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="43">
         <f>'Financial Model'!D7</f>
         <v>2036322</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="43">
         <f>'Financial Model'!E7</f>
         <v>2611708</v>
       </c>
-      <c r="F24" s="42">
+      <c r="F24" s="43">
         <f>'Financial Model'!F7</f>
         <v>3011257</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="30">
         <f>'Financial Model'!B8</f>
         <v>789764</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>'Financial Model'!C8</f>
         <v>2193156</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>'Financial Model'!D8</f>
         <v>4229478</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>'Financial Model'!E8</f>
         <v>6841186</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>'Financial Model'!F8</f>
         <v>9852443</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="34" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="13">
@@ -3412,7 +3436,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3421,83 +3445,83 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="B29" s="29">
+      <c r="A29" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>19750</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>20097.46153846154</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>20542.25</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>21054.324324324323</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>21615</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B30" s="41">
+      <c r="A30" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="42">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.4327959493670886</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="42">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.3271641653940222</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.26006523141330673</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.21945084145261293</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="42">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.1977265787647467</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="B31" s="41">
+      <c r="A31" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="42">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.13741772151898735</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="42">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.11882174174312102</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="42">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.10697525830909467</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="42">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.10000025673611379</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="42">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.0966705991209808</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>161</v>
+      <c r="A32" s="34" t="s">
+        <v>162</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
@@ -3522,7 +3546,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3531,62 +3555,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B35" s="41">
+      <c r="A35" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="42">
         <v>0.5675057208237986</v>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="42">
         <v>0.5732777238345675</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="42">
         <v>0.5768052612509744</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="42">
         <v>0.5789280554886744</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="42">
         <v>0.5801743191959632</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" s="41">
+      <c r="A36" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="42">
         <v>0.39816933638443935</v>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="42">
         <v>0.4025342174644695</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="42">
         <v>0.4053534765757952</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="42">
         <v>0.4071812549774971</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="42">
         <v>0.4083573126485675</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="41">
+      <c r="A37" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="42">
         <v>0.034324942791762014</v>
       </c>
-      <c r="C37" s="41">
+      <c r="C37" s="42">
         <v>0.02418805870096303</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="42">
         <v>0.01784126217323042</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="42">
         <v>0.01389068953382846</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="42">
         <v>0.01146836815546937</v>
       </c>
     </row>
@@ -3623,55 +3647,55 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="43">
+      <c r="A4" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="44">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="35">
+      <c r="A5" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="36">
         <v>1200000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="35">
+      <c r="A6" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="36">
         <v>1150000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" s="35">
+      <c r="A7" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="36">
         <v>75000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="35">
+      <c r="A8" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="36">
         <v>50000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B9" s="44">
+      <c r="A9" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="45">
         <v>0.8</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -13,6 +13,7 @@
     <sheet sheetId="6" name="Financial Model" state="visible" r:id="rId10"/>
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
     <sheet sheetId="8" name="Prior-Year Snapshot" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
@@ -31,13 +32,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Prior-Year Snapshot'!$A1:$B9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="227">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -553,21 +556,187 @@
   </si>
   <si>
     <t>Cash Reserve (Months)</t>
+  </si>
+  <si>
+    <t>Heritage Academy — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>60+ months</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 20% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 3% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 89.55x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>91.2 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0;#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -676,6 +845,24 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -779,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -828,11 +1015,222 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1428,6 +1826,679 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="50" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="51">
+        <v>100</v>
+      </c>
+      <c r="D7" s="51">
+        <v>130</v>
+      </c>
+      <c r="E7" s="51">
+        <v>160</v>
+      </c>
+      <c r="F7" s="51">
+        <v>185</v>
+      </c>
+      <c r="G7" s="51">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="52">
+        <v>1975000</v>
+      </c>
+      <c r="D8" s="52">
+        <v>2612670</v>
+      </c>
+      <c r="E8" s="52">
+        <v>3286760</v>
+      </c>
+      <c r="F8" s="52">
+        <v>3895050</v>
+      </c>
+      <c r="G8" s="52">
+        <v>4323000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="52">
+        <v>854772</v>
+      </c>
+      <c r="D9" s="52">
+        <v>854772</v>
+      </c>
+      <c r="E9" s="52">
+        <v>854772</v>
+      </c>
+      <c r="F9" s="52">
+        <v>854772</v>
+      </c>
+      <c r="G9" s="52">
+        <v>854772</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="52">
+        <v>271400</v>
+      </c>
+      <c r="D10" s="52">
+        <v>310442</v>
+      </c>
+      <c r="E10" s="52">
+        <v>351602</v>
+      </c>
+      <c r="F10" s="52">
+        <v>389506</v>
+      </c>
+      <c r="G10" s="52">
+        <v>417907</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="52">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="D11" s="52">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="E11" s="52">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="F11" s="52">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="G11" s="52">
+        <v>34064.39316600799</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="54">
+        <v>789764</v>
+      </c>
+      <c r="D12" s="54">
+        <v>1403392</v>
+      </c>
+      <c r="E12" s="54">
+        <v>2036322</v>
+      </c>
+      <c r="F12" s="54">
+        <v>2611708</v>
+      </c>
+      <c r="G12" s="54">
+        <v>3011257</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="54">
+        <v>864764</v>
+      </c>
+      <c r="D13" s="54">
+        <v>2268156</v>
+      </c>
+      <c r="E13" s="54">
+        <v>4304478</v>
+      </c>
+      <c r="F13" s="54">
+        <v>6916186</v>
+      </c>
+      <c r="G13" s="54">
+        <v>9927443</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="55">
+        <v>0.3998805063291139</v>
+      </c>
+      <c r="D14" s="55">
+        <v>0.5371485874603376</v>
+      </c>
+      <c r="E14" s="55">
+        <v>0.6195529944382918</v>
+      </c>
+      <c r="F14" s="55">
+        <v>0.6705197622623587</v>
+      </c>
+      <c r="G14" s="55">
+        <v>0.6965665047420773</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="56">
+        <v>19750</v>
+      </c>
+      <c r="D15" s="56">
+        <v>20097.46153846154</v>
+      </c>
+      <c r="E15" s="56">
+        <v>20542.25</v>
+      </c>
+      <c r="F15" s="56">
+        <v>21054.324324324323</v>
+      </c>
+      <c r="G15" s="56">
+        <v>21615</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" s="55">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D16" s="55">
+        <v>0.3271641653940222</v>
+      </c>
+      <c r="E16" s="55">
+        <v>0.26006523141330673</v>
+      </c>
+      <c r="F16" s="55">
+        <v>0.21945084145261293</v>
+      </c>
+      <c r="G16" s="55">
+        <v>0.1977265787647467</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="55">
+        <v>0.0412253164556962</v>
+      </c>
+      <c r="D17" s="55">
+        <v>0.035646522522936305</v>
+      </c>
+      <c r="E17" s="55">
+        <v>0.0320925774927284</v>
+      </c>
+      <c r="F17" s="55">
+        <v>0.030000077020834136</v>
+      </c>
+      <c r="G17" s="55">
+        <v>0.02900117973629424</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="55">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D18" s="55">
+        <v>0.5540140928628567</v>
+      </c>
+      <c r="E18" s="55">
+        <v>0.6329595102775986</v>
+      </c>
+      <c r="F18" s="55">
+        <v>0.6805489018112733</v>
+      </c>
+      <c r="G18" s="55">
+        <v>0.7056028221142725</v>
+      </c>
+      <c r="H18" s="57" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" s="58">
+        <v>4</v>
+      </c>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="57" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="59">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D20" s="59">
+        <v>42.49175944353473</v>
+      </c>
+      <c r="E20" s="59">
+        <v>61.07215795277884</v>
+      </c>
+      <c r="F20" s="59">
+        <v>77.81650437986194</v>
+      </c>
+      <c r="G20" s="59">
+        <v>89.54573137806075</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="57" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" s="63"/>
+      <c r="F25" s="64" t="s">
+        <v>206</v>
+      </c>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="E26" s="63"/>
+      <c r="F26" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27" s="63"/>
+      <c r="F27" s="64" t="s">
+        <v>212</v>
+      </c>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="61" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="63"/>
+      <c r="F28" s="64" t="s">
+        <v>215</v>
+      </c>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="63"/>
+      <c r="F29" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="61" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64" t="s">
+        <v>221</v>
+      </c>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="E31" s="63"/>
+      <c r="F31" s="64" t="s">
+        <v>224</v>
+      </c>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C14&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C14&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C14&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&gt;=10000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&gt;=7000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&lt;7000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BHeritage Academy&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="229">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -496,6 +496,12 @@
   </si>
   <si>
     <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>Financial Model Summary</t>
@@ -966,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1009,6 +1015,12 @@
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1045,9 +1057,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1843,118 +1852,118 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+      <c r="B3" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="47" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="49" t="s">
+      <c r="B4" s="49" t="s">
         <v>176</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="50" t="s">
-        <v>178</v>
+      <c r="H6" s="52" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="51">
+        <v>181</v>
+      </c>
+      <c r="C7" s="53">
         <v>100</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="53">
         <v>130</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="53">
         <v>160</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="53">
         <v>185</v>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="53">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="52">
+        <v>182</v>
+      </c>
+      <c r="C8" s="54">
         <v>1975000</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="54">
         <v>2612670</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="54">
         <v>3286760</v>
       </c>
-      <c r="F8" s="52">
+      <c r="F8" s="54">
         <v>3895050</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="54">
         <v>4323000</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="52">
+        <v>183</v>
+      </c>
+      <c r="C9" s="54">
         <v>854772</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="54">
         <v>854772</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="54">
         <v>854772</v>
       </c>
-      <c r="F9" s="52">
+      <c r="F9" s="54">
         <v>854772</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="54">
         <v>854772</v>
       </c>
     </row>
@@ -1962,419 +1971,419 @@
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="52">
+      <c r="C10" s="54">
         <v>271400</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="54">
         <v>310442</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="54">
         <v>351602</v>
       </c>
-      <c r="F10" s="52">
+      <c r="F10" s="54">
         <v>389506</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="54">
         <v>417907</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="52">
+        <v>184</v>
+      </c>
+      <c r="C11" s="54">
         <v>34064.39316600799</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="54">
         <v>34064.39316600799</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="54">
         <v>34064.39316600799</v>
       </c>
-      <c r="F11" s="52">
+      <c r="F11" s="54">
         <v>34064.39316600799</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="54">
         <v>34064.39316600799</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="56">
         <v>789764</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="56">
         <v>1403392</v>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="56">
         <v>2036322</v>
       </c>
-      <c r="F12" s="54">
+      <c r="F12" s="56">
         <v>2611708</v>
       </c>
-      <c r="G12" s="54">
+      <c r="G12" s="56">
         <v>3011257</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="53" t="s">
-        <v>183</v>
-      </c>
-      <c r="C13" s="54">
+      <c r="B13" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="56">
         <v>864764</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="56">
         <v>2268156</v>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="56">
         <v>4304478</v>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="56">
         <v>6916186</v>
       </c>
-      <c r="G13" s="54">
+      <c r="G13" s="56">
         <v>9927443</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="C14" s="55">
+      <c r="B14" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="57">
         <v>0.3998805063291139</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="57">
         <v>0.5371485874603376</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="57">
         <v>0.6195529944382918</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="57">
         <v>0.6705197622623587</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="57">
         <v>0.6965665047420773</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="56">
+      <c r="B15" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="58">
         <v>19750</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="58">
         <v>20097.46153846154</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="58">
         <v>20542.25</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="58">
         <v>21054.324324324323</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="58">
         <v>21615</v>
       </c>
-      <c r="H15" s="57" t="s">
-        <v>185</v>
+      <c r="H15" s="59" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="53" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" s="55">
+      <c r="B16" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="57">
         <v>0.4327959493670886</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="57">
         <v>0.3271641653940222</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="57">
         <v>0.26006523141330673</v>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="57">
         <v>0.21945084145261293</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="57">
         <v>0.1977265787647467</v>
       </c>
-      <c r="H16" s="57" t="s">
-        <v>187</v>
+      <c r="H16" s="59" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="55">
+      <c r="B17" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="57">
         <v>0.0412253164556962</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="57">
         <v>0.035646522522936305</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="57">
         <v>0.0320925774927284</v>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="57">
         <v>0.030000077020834136</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="57">
         <v>0.02900117973629424</v>
       </c>
-      <c r="H17" s="57" t="s">
-        <v>189</v>
+      <c r="H17" s="59" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="55">
+      <c r="B18" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="57">
         <v>0.42978632911392406</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="57">
         <v>0.5540140928628567</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="57">
         <v>0.6329595102775986</v>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="57">
         <v>0.6805489018112733</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="57">
         <v>0.7056028221142725</v>
       </c>
-      <c r="H18" s="57" t="s">
-        <v>191</v>
+      <c r="H18" s="59" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="53" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="58">
+      <c r="B19" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="60">
         <v>4</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="57" t="s">
-        <v>193</v>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="59" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="C20" s="59">
+      <c r="B20" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="61">
         <v>24.918336160088252</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="61">
         <v>42.49175944353473</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="61">
         <v>61.07215795277884</v>
       </c>
-      <c r="F20" s="59">
+      <c r="F20" s="61">
         <v>77.81650437986194</v>
       </c>
-      <c r="G20" s="59">
+      <c r="G20" s="61">
         <v>89.54573137806075</v>
       </c>
-      <c r="H20" s="57" t="s">
-        <v>195</v>
+      <c r="H20" s="59" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C21" s="60" t="s">
+      <c r="B21" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="57" t="s">
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="59" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="57" t="s">
-        <v>198</v>
+      <c r="B22" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="59" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="C25" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D25" s="63" t="s">
+      <c r="B25" s="63" t="s">
         <v>205</v>
       </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64" t="s">
+      <c r="C25" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
+      <c r="D25" s="64" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" s="64"/>
+      <c r="F25" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
-        <v>207</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D26" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64" t="s">
+      <c r="B26" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
+      <c r="C26" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" s="64"/>
+      <c r="F26" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D27" s="63" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="64" t="s">
+      <c r="B27" s="63" t="s">
         <v>212</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="C27" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D27" s="64" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="64"/>
+      <c r="F27" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D28" s="63" t="s">
-        <v>214</v>
-      </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64" t="s">
+      <c r="B28" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
+      <c r="C28" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="E28" s="64"/>
+      <c r="F28" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="61" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D29" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64" t="s">
+      <c r="B29" s="63" t="s">
         <v>218</v>
       </c>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
+      <c r="C29" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="64" t="s">
+        <v>219</v>
+      </c>
+      <c r="E29" s="64"/>
+      <c r="F29" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
-        <v>219</v>
-      </c>
-      <c r="C30" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D30" s="63" t="s">
-        <v>220</v>
-      </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
+      <c r="B30" s="63" t="s">
         <v>221</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
+      <c r="C30" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" s="64"/>
+      <c r="F30" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D31" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64" t="s">
+      <c r="B31" s="63" t="s">
         <v>224</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
+      <c r="C31" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="64" t="s">
+        <v>225</v>
+      </c>
+      <c r="E31" s="64"/>
+      <c r="F31" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="53" t="s">
-        <v>225</v>
-      </c>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
+      <c r="C33" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
-        <v>226</v>
-      </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
+      <c r="B35" s="66" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -3893,7 +3902,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -4118,6 +4127,26 @@
       <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>90.1314632515668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4143,18 +4172,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="A1" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
-        <v>153</v>
+      <c r="A2" s="43" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4228,12 +4257,12 @@
         <v>41</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -4288,24 +4317,24 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="42">
+        <v>159</v>
+      </c>
+      <c r="C17" s="44">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.3</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="44">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="44">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.15625</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="44">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.08108108108108109</v>
       </c>
@@ -4434,23 +4463,23 @@
       <c r="A24" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="43">
+      <c r="B24" s="45">
         <f>'Financial Model'!B7</f>
         <v>789764</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="45">
         <f>'Financial Model'!C7</f>
         <v>1403392</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="45">
         <f>'Financial Model'!D7</f>
         <v>2036322</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="45">
         <f>'Financial Model'!E7</f>
         <v>2611708</v>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="45">
         <f>'Financial Model'!F7</f>
         <v>3011257</v>
       </c>
@@ -4507,7 +4536,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -4517,7 +4546,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
@@ -4542,57 +4571,57 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B30" s="42">
+        <v>162</v>
+      </c>
+      <c r="B30" s="44">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.4327959493670886</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="44">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.3271641653940222</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="44">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.26006523141330673</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="44">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.21945084145261293</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="44">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.1977265787647467</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31" s="42">
+        <v>163</v>
+      </c>
+      <c r="B31" s="44">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.13741772151898735</v>
       </c>
-      <c r="C31" s="42">
+      <c r="C31" s="44">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.11882174174312102</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="44">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.10697525830909467</v>
       </c>
-      <c r="E31" s="42">
+      <c r="E31" s="44">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.10000025673611379</v>
       </c>
-      <c r="F31" s="42">
+      <c r="F31" s="44">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.0966705991209808</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
@@ -4617,7 +4646,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -4627,61 +4656,61 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B35" s="42">
+        <v>166</v>
+      </c>
+      <c r="B35" s="44">
         <v>0.5675057208237986</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="44">
         <v>0.5732777238345675</v>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="44">
         <v>0.5768052612509744</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="44">
         <v>0.5789280554886744</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="44">
         <v>0.5801743191959632</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B36" s="42">
+        <v>167</v>
+      </c>
+      <c r="B36" s="44">
         <v>0.39816933638443935</v>
       </c>
-      <c r="C36" s="42">
+      <c r="C36" s="44">
         <v>0.4025342174644695</v>
       </c>
-      <c r="D36" s="42">
+      <c r="D36" s="44">
         <v>0.4053534765757952</v>
       </c>
-      <c r="E36" s="42">
+      <c r="E36" s="44">
         <v>0.4071812549774971</v>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="44">
         <v>0.4083573126485675</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B37" s="42">
+        <v>168</v>
+      </c>
+      <c r="B37" s="44">
         <v>0.034324942791762014</v>
       </c>
-      <c r="C37" s="42">
+      <c r="C37" s="44">
         <v>0.02418805870096303</v>
       </c>
-      <c r="D37" s="42">
+      <c r="D37" s="44">
         <v>0.01784126217323042</v>
       </c>
-      <c r="E37" s="42">
+      <c r="E37" s="44">
         <v>0.01389068953382846</v>
       </c>
-      <c r="F37" s="42">
+      <c r="F37" s="44">
         <v>0.01146836815546937</v>
       </c>
     </row>
@@ -4718,15 +4747,15 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="44">
+        <v>170</v>
+      </c>
+      <c r="B4" s="46">
         <v>85</v>
       </c>
     </row>
@@ -4748,7 +4777,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B7" s="36">
         <v>75000</v>
@@ -4756,7 +4785,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B8" s="36">
         <v>50000</v>
@@ -4764,9 +4793,9 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="B9" s="45">
+        <v>173</v>
+      </c>
+      <c r="B9" s="47">
         <v>0.8</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -2493,10 +2493,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="229">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -972,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1054,6 +1054,9 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2201,13 +2204,26 @@
       <c r="B21" s="55" t="s">
         <v>198</v>
       </c>
-      <c r="C21" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
+      <c r="C21" s="40" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="62" t="str">
+        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="62" t="str">
+        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="62" t="str">
+        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="62" t="str">
+        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="59" t="s">
         <v>68</v>
       </c>
@@ -2216,13 +2232,13 @@
       <c r="B22" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="63" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
       <c r="H22" s="59" t="s">
         <v>200</v>
       </c>
@@ -2245,126 +2261,126 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="64" t="s">
         <v>205</v>
       </c>
       <c r="C25" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="E25" s="64"/>
-      <c r="F25" s="65" t="s">
+      <c r="E25" s="65"/>
+      <c r="F25" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="64" t="s">
         <v>209</v>
       </c>
       <c r="C26" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="E26" s="64"/>
-      <c r="F26" s="65" t="s">
+      <c r="E26" s="65"/>
+      <c r="F26" s="66" t="s">
         <v>211</v>
       </c>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="64" t="s">
         <v>212</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65" t="s">
+      <c r="E27" s="65"/>
+      <c r="F27" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="64" t="s">
         <v>215</v>
       </c>
       <c r="C28" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="E28" s="64"/>
-      <c r="F28" s="65" t="s">
+      <c r="E28" s="65"/>
+      <c r="F28" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="64" t="s">
         <v>218</v>
       </c>
       <c r="C29" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E29" s="64"/>
-      <c r="F29" s="65" t="s">
+      <c r="E29" s="65"/>
+      <c r="F29" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="64" t="s">
         <v>221</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D30" s="64" t="s">
+      <c r="D30" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="65" t="s">
+      <c r="E30" s="65"/>
+      <c r="F30" s="66" t="s">
         <v>223</v>
       </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="64" t="s">
         <v>224</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D31" s="64" t="s">
+      <c r="D31" s="65" t="s">
         <v>225</v>
       </c>
-      <c r="E31" s="64"/>
-      <c r="F31" s="65" t="s">
+      <c r="E31" s="65"/>
+      <c r="F31" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="64" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="55" t="s">
@@ -2375,22 +2391,21 @@
       <c r="F33" s="55"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -2471,10 +2486,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="230">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -639,10 +639,13 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>60+</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -870,7 +873,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -900,6 +903,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -972,7 +985,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1051,14 +1064,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2169,10 +2192,18 @@
       <c r="C19" s="60">
         <v>4</v>
       </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
+      <c r="D19" s="60">
+        <v>4</v>
+      </c>
+      <c r="E19" s="60">
+        <v>4</v>
+      </c>
+      <c r="F19" s="60">
+        <v>4</v>
+      </c>
+      <c r="G19" s="60">
+        <v>4</v>
+      </c>
       <c r="H19" s="59" t="s">
         <v>195</v>
       </c>
@@ -2209,19 +2240,19 @@
         <v>✓ Break-even</v>
       </c>
       <c r="D21" s="62" t="str">
-        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="62" t="str">
-        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="62" t="str">
-        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="62" t="str">
-        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="59" t="s">
@@ -2232,181 +2263,187 @@
       <c r="B22" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="63">
+        <v>9</v>
+      </c>
+      <c r="D22" s="64">
+        <v>23</v>
+      </c>
+      <c r="E22" s="60">
+        <v>42</v>
+      </c>
+      <c r="F22" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
+      <c r="G22" s="65" t="s">
+        <v>200</v>
+      </c>
       <c r="H22" s="59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
-        <v>205</v>
+      <c r="B25" s="66" t="s">
+        <v>206</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66" t="s">
+      <c r="D25" s="67" t="s">
         <v>208</v>
       </c>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68" t="s">
+        <v>209</v>
+      </c>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="64" t="s">
-        <v>209</v>
+      <c r="B26" s="66" t="s">
+        <v>210</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" s="65" t="s">
-        <v>210</v>
-      </c>
-      <c r="E26" s="65"/>
-      <c r="F26" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D26" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="68" t="s">
+        <v>212</v>
+      </c>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
-        <v>212</v>
+      <c r="B27" s="66" t="s">
+        <v>213</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" s="65" t="s">
-        <v>213</v>
-      </c>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="64" t="s">
-        <v>215</v>
+      <c r="B28" s="66" t="s">
+        <v>216</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D28" s="65" t="s">
-        <v>216</v>
-      </c>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D28" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="64" t="s">
-        <v>218</v>
+      <c r="B29" s="66" t="s">
+        <v>219</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="65" t="s">
-        <v>219</v>
-      </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D29" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="64" t="s">
-        <v>221</v>
+      <c r="B30" s="66" t="s">
+        <v>222</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D30" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="64" t="s">
-        <v>224</v>
+      <c r="B31" s="66" t="s">
+        <v>225</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="65" t="s">
-        <v>225</v>
-      </c>
-      <c r="E31" s="65"/>
-      <c r="F31" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
+      <c r="B33" s="66" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D33" s="55"/>
       <c r="E33" s="55"/>
       <c r="F33" s="55"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="C35" s="67"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
+      <c r="B35" s="69" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -693,7 +693,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 3% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -2144,19 +2144,19 @@
         <v>190</v>
       </c>
       <c r="C17" s="57">
-        <v>0.0412253164556962</v>
+        <v>0.0690632911392405</v>
       </c>
       <c r="D17" s="57">
-        <v>0.035646522522936305</v>
+        <v>0.053773342978638713</v>
       </c>
       <c r="E17" s="57">
-        <v>0.0320925774927284</v>
+        <v>0.04402688361790943</v>
       </c>
       <c r="F17" s="57">
-        <v>0.030000077020834136</v>
+        <v>0.038265273616513266</v>
       </c>
       <c r="G17" s="57">
-        <v>0.02900117973629424</v>
+        <v>0.0355105016470044</v>
       </c>
       <c r="H17" s="59" t="s">
         <v>191</v>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -567,7 +567,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -2876,25 +2876,25 @@
       <c r="A16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="31" t="str">
+      <c r="B16" s="31">
         <f>SUM(B14:B15)</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="31" t="str">
+        <v>75000</v>
+      </c>
+      <c r="C16" s="31">
         <f>SUM(C14:C15)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="31" t="str">
+        <v>70000</v>
+      </c>
+      <c r="D16" s="31">
         <f>SUM(D14:D15)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="31" t="str">
+        <v>65000</v>
+      </c>
+      <c r="E16" s="31">
         <f>SUM(E14:E15)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="31" t="str">
+        <v>60000</v>
+      </c>
+      <c r="F16" s="31">
         <f>SUM(F14:F15)</f>
-        <v>0</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Prior-Year Snapshot'!$A1:$B9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="232">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -646,6 +646,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1867,7 +1873,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2282,170 +2288,191 @@
         <v>201</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C23" s="60">
+        <v>272</v>
+      </c>
+      <c r="D23" s="60">
+        <v>690</v>
+      </c>
+      <c r="E23" s="60">
+        <v>1267</v>
+      </c>
+      <c r="F23" s="60">
+        <v>1975</v>
+      </c>
+      <c r="G23" s="60">
+        <v>2773</v>
+      </c>
+      <c r="H23" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="D24" s="8" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="66" t="s">
+      <c r="D25" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="D25" s="67" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68" t="s">
-        <v>209</v>
-      </c>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="66" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="67" t="s">
         <v>210</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D26" s="67" t="s">
-        <v>211</v>
       </c>
       <c r="E26" s="67"/>
       <c r="F26" s="68" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G26" s="68"/>
       <c r="H26" s="68"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="66" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="67" t="s">
         <v>213</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D27" s="67" t="s">
-        <v>214</v>
       </c>
       <c r="E27" s="67"/>
       <c r="F27" s="68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G27" s="68"/>
       <c r="H27" s="68"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="66" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D28" s="67" t="s">
         <v>216</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D28" s="67" t="s">
-        <v>217</v>
       </c>
       <c r="E28" s="67"/>
       <c r="F28" s="68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G28" s="68"/>
       <c r="H28" s="68"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="66" t="s">
+        <v>218</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" s="67" t="s">
         <v>219</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D29" s="67" t="s">
-        <v>220</v>
       </c>
       <c r="E29" s="67"/>
       <c r="F29" s="68" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G29" s="68"/>
       <c r="H29" s="68"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" s="67" t="s">
         <v>222</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D30" s="67" t="s">
-        <v>223</v>
       </c>
       <c r="E30" s="67"/>
       <c r="F30" s="68" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G30" s="68"/>
       <c r="H30" s="68"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="66" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="67" t="s">
         <v>225</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D31" s="67" t="s">
-        <v>226</v>
       </c>
       <c r="E31" s="67"/>
       <c r="F31" s="68" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G31" s="68"/>
       <c r="H31" s="68"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="66" t="s">
+        <v>227</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D32" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="E32" s="67"/>
+      <c r="F32" s="68" t="s">
+        <v>229</v>
+      </c>
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="55" t="s">
-        <v>228</v>
-      </c>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="69" t="s">
-        <v>229</v>
-      </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
+      <c r="C34" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -2460,8 +2487,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Prior-Year Snapshot'!$A1:$B9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="237">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -604,6 +604,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -991,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1070,6 +1085,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1873,7 +1894,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2122,365 +2143,440 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="57">
-        <v>0.4327959493670886</v>
-      </c>
-      <c r="D16" s="57">
-        <v>0.3271641653940222</v>
-      </c>
-      <c r="E16" s="57">
-        <v>0.26006523141330673</v>
-      </c>
-      <c r="F16" s="57">
-        <v>0.21945084145261293</v>
-      </c>
-      <c r="G16" s="57">
-        <v>0.1977265787647467</v>
-      </c>
-      <c r="H16" s="59" t="s">
+      <c r="C16" s="60">
+        <v>11602.36393166008</v>
+      </c>
+      <c r="D16" s="60">
+        <v>9225.218408969291</v>
+      </c>
+      <c r="E16" s="60">
+        <v>7752.739957287549</v>
+      </c>
+      <c r="F16" s="60">
+        <v>6909.958881978421</v>
+      </c>
+      <c r="G16" s="60">
+        <v>6533.71696583004</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="55" t="s">
+      <c r="C17" s="54">
+        <v>600</v>
+      </c>
+      <c r="D17" s="54">
+        <v>618</v>
+      </c>
+      <c r="E17" s="54">
+        <v>637</v>
+      </c>
+      <c r="F17" s="54">
+        <v>656</v>
+      </c>
+      <c r="G17" s="54">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="57">
-        <v>0.0690632911392405</v>
-      </c>
-      <c r="D17" s="57">
-        <v>0.053773342978638713</v>
-      </c>
-      <c r="E17" s="57">
-        <v>0.04402688361790943</v>
-      </c>
-      <c r="F17" s="57">
-        <v>0.038265273616513266</v>
-      </c>
-      <c r="G17" s="57">
-        <v>0.0355105016470044</v>
-      </c>
-      <c r="H17" s="59" t="s">
+      <c r="C18" s="58">
+        <v>1364</v>
+      </c>
+      <c r="D18" s="58">
+        <v>1080.7076923076922</v>
+      </c>
+      <c r="E18" s="58">
+        <v>904.4112499999999</v>
+      </c>
+      <c r="F18" s="58">
+        <v>805.6494810810811</v>
+      </c>
+      <c r="G18" s="58">
+        <v>767.5594931</v>
+      </c>
+      <c r="H18" s="59" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="55" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="55" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="57">
-        <v>0.42978632911392406</v>
-      </c>
-      <c r="D18" s="57">
-        <v>0.5540140928628567</v>
-      </c>
-      <c r="E18" s="57">
-        <v>0.6329595102775986</v>
-      </c>
-      <c r="F18" s="57">
-        <v>0.6805489018112733</v>
-      </c>
-      <c r="G18" s="57">
-        <v>0.7056028221142725</v>
-      </c>
-      <c r="H18" s="59" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="60">
-        <v>4</v>
-      </c>
-      <c r="D19" s="60">
-        <v>4</v>
-      </c>
-      <c r="E19" s="60">
-        <v>4</v>
-      </c>
-      <c r="F19" s="60">
-        <v>4</v>
-      </c>
-      <c r="G19" s="60">
-        <v>4</v>
-      </c>
-      <c r="H19" s="59" t="s">
-        <v>195</v>
+      <c r="C19" s="61">
+        <v>7897.64</v>
+      </c>
+      <c r="D19" s="61">
+        <v>10795.323076923078</v>
+      </c>
+      <c r="E19" s="61">
+        <v>12727.0125</v>
+      </c>
+      <c r="F19" s="61">
+        <v>14117.340540540541</v>
+      </c>
+      <c r="G19" s="61">
+        <v>15056.285</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="61">
-        <v>24.918336160088252</v>
-      </c>
-      <c r="D20" s="61">
-        <v>42.49175944353473</v>
-      </c>
-      <c r="E20" s="61">
-        <v>61.07215795277884</v>
-      </c>
-      <c r="F20" s="61">
-        <v>77.81650437986194</v>
-      </c>
-      <c r="G20" s="61">
-        <v>89.54573137806075</v>
+        <v>193</v>
+      </c>
+      <c r="C20" s="57">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D20" s="57">
+        <v>0.3271641653940222</v>
+      </c>
+      <c r="E20" s="57">
+        <v>0.26006523141330673</v>
+      </c>
+      <c r="F20" s="57">
+        <v>0.21945084145261293</v>
+      </c>
+      <c r="G20" s="57">
+        <v>0.1977265787647467</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="57">
+        <v>0.0690632911392405</v>
+      </c>
+      <c r="D21" s="57">
+        <v>0.053773342978638713</v>
+      </c>
+      <c r="E21" s="57">
+        <v>0.04402688361790943</v>
+      </c>
+      <c r="F21" s="57">
+        <v>0.038265273616513266</v>
+      </c>
+      <c r="G21" s="57">
+        <v>0.0355105016470044</v>
+      </c>
+      <c r="H21" s="59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="57">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D22" s="57">
+        <v>0.5540140928628567</v>
+      </c>
+      <c r="E22" s="57">
+        <v>0.6329595102775986</v>
+      </c>
+      <c r="F22" s="57">
+        <v>0.6805489018112733</v>
+      </c>
+      <c r="G22" s="57">
+        <v>0.7056028221142725</v>
+      </c>
+      <c r="H22" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="C21" s="40" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="62">
+        <v>4</v>
+      </c>
+      <c r="D23" s="62">
+        <v>4</v>
+      </c>
+      <c r="E23" s="62">
+        <v>4</v>
+      </c>
+      <c r="F23" s="62">
+        <v>4</v>
+      </c>
+      <c r="G23" s="62">
+        <v>4</v>
+      </c>
+      <c r="H23" s="59" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="63">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D24" s="63">
+        <v>42.49175944353473</v>
+      </c>
+      <c r="E24" s="63">
+        <v>61.07215795277884</v>
+      </c>
+      <c r="F24" s="63">
+        <v>77.81650437986194</v>
+      </c>
+      <c r="G24" s="63">
+        <v>89.54573137806075</v>
+      </c>
+      <c r="H24" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="62" t="str">
+      <c r="D25" s="64" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="62" t="str">
+      <c r="E25" s="64" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="62" t="str">
+      <c r="F25" s="64" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="62" t="str">
+      <c r="G25" s="64" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="59" t="s">
+      <c r="H25" s="59" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="55" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="63">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" s="65">
         <v>9</v>
       </c>
-      <c r="D22" s="64">
+      <c r="D26" s="66">
         <v>23</v>
       </c>
-      <c r="E22" s="60">
+      <c r="E26" s="62">
         <v>42</v>
       </c>
-      <c r="F22" s="65" t="s">
-        <v>200</v>
-      </c>
-      <c r="G22" s="65" t="s">
-        <v>200</v>
-      </c>
-      <c r="H22" s="59" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
-        <v>202</v>
-      </c>
-      <c r="C23" s="60">
+      <c r="F26" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="H26" s="59" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="62">
         <v>272</v>
       </c>
-      <c r="D23" s="60">
+      <c r="D27" s="62">
         <v>690</v>
       </c>
-      <c r="E23" s="60">
+      <c r="E27" s="62">
         <v>1267</v>
       </c>
-      <c r="F23" s="60">
+      <c r="F27" s="62">
         <v>1975</v>
       </c>
-      <c r="G23" s="60">
+      <c r="G27" s="62">
         <v>2773</v>
       </c>
-      <c r="H23" s="59" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="66" t="s">
+      <c r="H27" s="59" t="s">
         <v>208</v>
       </c>
-      <c r="C26" s="40" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D26" s="67" t="s">
+      <c r="C29" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68" t="s">
+      <c r="D29" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="66" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C27" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="D27" s="67" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68" t="s">
+      <c r="C30" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="G27" s="68"/>
-      <c r="H27" s="68"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="66" t="s">
+      <c r="D30" s="69" t="s">
         <v>215</v>
       </c>
-      <c r="C28" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="D28" s="67" t="s">
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
         <v>216</v>
       </c>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68" t="s">
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="G28" s="68"/>
-      <c r="H28" s="68"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="66" t="s">
+      <c r="C31" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D31" s="69" t="s">
         <v>218</v>
       </c>
-      <c r="C29" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="D29" s="67" t="s">
+      <c r="E31" s="69"/>
+      <c r="F31" s="70" t="s">
         <v>219</v>
       </c>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68" t="s">
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
+      <c r="C32" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="D30" s="67" t="s">
+      <c r="E32" s="69"/>
+      <c r="F32" s="70" t="s">
         <v>222</v>
       </c>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68" t="s">
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
+      <c r="C33" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D33" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="D31" s="67" t="s">
+      <c r="E33" s="69"/>
+      <c r="F33" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="E31" s="67"/>
-      <c r="F31" s="68" t="s">
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="66" t="s">
+      <c r="C34" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D34" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="C32" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="D32" s="67" t="s">
+      <c r="E34" s="69"/>
+      <c r="F34" s="70" t="s">
         <v>228</v>
       </c>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68" t="s">
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="68" t="s">
         <v>229</v>
       </c>
-      <c r="G32" s="68"/>
-      <c r="H32" s="68"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="66" t="s">
+      <c r="C35" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>230</v>
+      </c>
+      <c r="E35" s="69"/>
+      <c r="F35" s="70" t="s">
+        <v>231</v>
+      </c>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="69" t="s">
+        <v>233</v>
+      </c>
+      <c r="E36" s="69"/>
+      <c r="F36" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="55" t="s">
-        <v>230</v>
-      </c>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="69" t="s">
-        <v>231</v>
-      </c>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
+      <c r="C38" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="71" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -2489,8 +2585,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2536,48 +2640,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Prior-Year Snapshot'!$A1:$B9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="230">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -606,21 +606,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -661,12 +646,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1006,7 +985,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1085,12 +1064,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1894,7 +1867,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2143,458 +2116,352 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="60">
-        <v>11602.36393166008</v>
-      </c>
-      <c r="D16" s="60">
-        <v>9225.218408969291</v>
-      </c>
-      <c r="E16" s="60">
-        <v>7752.739957287549</v>
-      </c>
-      <c r="F16" s="60">
-        <v>6909.958881978421</v>
-      </c>
-      <c r="G16" s="60">
-        <v>6533.71696583004</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="C16" s="57">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D16" s="57">
+        <v>0.3271641653940222</v>
+      </c>
+      <c r="E16" s="57">
+        <v>0.26006523141330673</v>
+      </c>
+      <c r="F16" s="57">
+        <v>0.21945084145261293</v>
+      </c>
+      <c r="G16" s="57">
+        <v>0.1977265787647467</v>
+      </c>
+      <c r="H16" s="59" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="54">
-        <v>600</v>
-      </c>
-      <c r="D17" s="54">
-        <v>618</v>
-      </c>
-      <c r="E17" s="54">
-        <v>637</v>
-      </c>
-      <c r="F17" s="54">
-        <v>656</v>
-      </c>
-      <c r="G17" s="54">
-        <v>675</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="57">
+        <v>0.0690632911392405</v>
+      </c>
+      <c r="D17" s="57">
+        <v>0.053773342978638713</v>
+      </c>
+      <c r="E17" s="57">
+        <v>0.04402688361790943</v>
+      </c>
+      <c r="F17" s="57">
+        <v>0.038265273616513266</v>
+      </c>
+      <c r="G17" s="57">
+        <v>0.0355105016470044</v>
+      </c>
+      <c r="H17" s="59" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="58">
-        <v>1364</v>
-      </c>
-      <c r="D18" s="58">
-        <v>1080.7076923076922</v>
-      </c>
-      <c r="E18" s="58">
-        <v>904.4112499999999</v>
-      </c>
-      <c r="F18" s="58">
-        <v>805.6494810810811</v>
-      </c>
-      <c r="G18" s="58">
-        <v>767.5594931</v>
+      <c r="B18" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="57">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D18" s="57">
+        <v>0.5540140928628567</v>
+      </c>
+      <c r="E18" s="57">
+        <v>0.6329595102775986</v>
+      </c>
+      <c r="F18" s="57">
+        <v>0.6805489018112733</v>
+      </c>
+      <c r="G18" s="57">
+        <v>0.7056028221142725</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="61">
-        <v>7897.64</v>
-      </c>
-      <c r="D19" s="61">
-        <v>10795.323076923078</v>
-      </c>
-      <c r="E19" s="61">
-        <v>12727.0125</v>
-      </c>
-      <c r="F19" s="61">
-        <v>14117.340540540541</v>
-      </c>
-      <c r="G19" s="61">
-        <v>15056.285</v>
+        <v>194</v>
+      </c>
+      <c r="C19" s="60">
+        <v>4</v>
+      </c>
+      <c r="D19" s="60">
+        <v>4</v>
+      </c>
+      <c r="E19" s="60">
+        <v>4</v>
+      </c>
+      <c r="F19" s="60">
+        <v>4</v>
+      </c>
+      <c r="G19" s="60">
+        <v>4</v>
+      </c>
+      <c r="H19" s="59" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="C20" s="57">
-        <v>0.4327959493670886</v>
-      </c>
-      <c r="D20" s="57">
-        <v>0.3271641653940222</v>
-      </c>
-      <c r="E20" s="57">
-        <v>0.26006523141330673</v>
-      </c>
-      <c r="F20" s="57">
-        <v>0.21945084145261293</v>
-      </c>
-      <c r="G20" s="57">
-        <v>0.1977265787647467</v>
+        <v>196</v>
+      </c>
+      <c r="C20" s="61">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D20" s="61">
+        <v>42.49175944353473</v>
+      </c>
+      <c r="E20" s="61">
+        <v>61.07215795277884</v>
+      </c>
+      <c r="F20" s="61">
+        <v>77.81650437986194</v>
+      </c>
+      <c r="G20" s="61">
+        <v>89.54573137806075</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="55" t="s">
-        <v>195</v>
-      </c>
-      <c r="C21" s="57">
-        <v>0.0690632911392405</v>
-      </c>
-      <c r="D21" s="57">
-        <v>0.053773342978638713</v>
-      </c>
-      <c r="E21" s="57">
-        <v>0.04402688361790943</v>
-      </c>
-      <c r="F21" s="57">
-        <v>0.038265273616513266</v>
-      </c>
-      <c r="G21" s="57">
-        <v>0.0355105016470044</v>
+        <v>198</v>
+      </c>
+      <c r="C21" s="40" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="62" t="str">
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="62" t="str">
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="62" t="str">
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="62" t="str">
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="59" t="s">
-        <v>196</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="55" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="57">
-        <v>0.42978632911392406</v>
-      </c>
-      <c r="D22" s="57">
-        <v>0.5540140928628567</v>
-      </c>
-      <c r="E22" s="57">
-        <v>0.6329595102775986</v>
-      </c>
-      <c r="F22" s="57">
-        <v>0.6805489018112733</v>
-      </c>
-      <c r="G22" s="57">
-        <v>0.7056028221142725</v>
+        <v>199</v>
+      </c>
+      <c r="C22" s="63">
+        <v>9</v>
+      </c>
+      <c r="D22" s="64">
+        <v>23</v>
+      </c>
+      <c r="E22" s="60">
+        <v>42</v>
+      </c>
+      <c r="F22" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="G22" s="65" t="s">
+        <v>200</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" s="62">
-        <v>4</v>
-      </c>
-      <c r="D23" s="62">
-        <v>4</v>
-      </c>
-      <c r="E23" s="62">
-        <v>4</v>
-      </c>
-      <c r="F23" s="62">
-        <v>4</v>
-      </c>
-      <c r="G23" s="62">
-        <v>4</v>
-      </c>
-      <c r="H23" s="59" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="C24" s="63">
-        <v>24.918336160088252</v>
-      </c>
-      <c r="D24" s="63">
-        <v>42.49175944353473</v>
-      </c>
-      <c r="E24" s="63">
-        <v>61.07215795277884</v>
-      </c>
-      <c r="F24" s="63">
-        <v>77.81650437986194</v>
-      </c>
-      <c r="G24" s="63">
-        <v>89.54573137806075</v>
-      </c>
-      <c r="H24" s="59" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
+      <c r="C24" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="40" t="str">
-        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="64" t="str">
-        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="64" t="str">
-        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="64" t="str">
-        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="64" t="str">
-        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="59" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="55" t="s">
+      <c r="D24" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="65">
-        <v>9</v>
-      </c>
-      <c r="D26" s="66">
-        <v>23</v>
-      </c>
-      <c r="E26" s="62">
-        <v>42</v>
-      </c>
-      <c r="F26" s="67" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="G26" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="H26" s="59" t="s">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="66" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
+      <c r="C25" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="C27" s="62">
-        <v>272</v>
-      </c>
-      <c r="D27" s="62">
-        <v>690</v>
-      </c>
-      <c r="E27" s="62">
-        <v>1267</v>
-      </c>
-      <c r="F27" s="62">
-        <v>1975</v>
-      </c>
-      <c r="G27" s="62">
-        <v>2773</v>
-      </c>
-      <c r="H27" s="59" t="s">
+      <c r="D25" s="67" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="E25" s="67"/>
+      <c r="F25" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="C26" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D26" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
+      <c r="E26" s="67"/>
+      <c r="F26" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="66" t="s">
+        <v>213</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="E27" s="67"/>
+      <c r="F27" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="66" t="s">
+        <v>216</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D28" s="67" t="s">
+        <v>217</v>
+      </c>
+      <c r="E28" s="67"/>
+      <c r="F28" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D29" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" s="67"/>
+      <c r="F29" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
-        <v>213</v>
+      <c r="B30" s="66" t="s">
+        <v>222</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>215</v>
-      </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
-        <v>216</v>
-      </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
+        <v>207</v>
+      </c>
+      <c r="D30" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="E30" s="67"/>
+      <c r="F30" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="68" t="s">
-        <v>217</v>
+      <c r="B31" s="66" t="s">
+        <v>225</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D31" s="69" t="s">
-        <v>218</v>
-      </c>
-      <c r="E31" s="69"/>
-      <c r="F31" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D32" s="69" t="s">
-        <v>221</v>
-      </c>
-      <c r="E32" s="69"/>
-      <c r="F32" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
-        <v>223</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D33" s="69" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="69"/>
-      <c r="F33" s="70" t="s">
-        <v>225</v>
-      </c>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="C34" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="69" t="s">
+      <c r="E31" s="67"/>
+      <c r="F31" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="E34" s="69"/>
-      <c r="F34" s="70" t="s">
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="68" t="s">
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="69" t="s">
         <v>229</v>
       </c>
-      <c r="C35" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D35" s="69" t="s">
-        <v>230</v>
-      </c>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
       <c r="E35" s="69"/>
-      <c r="F35" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="68" t="s">
-        <v>232</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="D36" s="69" t="s">
-        <v>233</v>
-      </c>
-      <c r="E36" s="69"/>
-      <c r="F36" s="70" t="s">
-        <v>234</v>
-      </c>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="68" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="71" t="s">
-        <v>236</v>
-      </c>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2640,48 +2507,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Prior-Year Snapshot'!$A1:$B9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="237">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -606,6 +606,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -646,6 +661,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -985,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1064,6 +1085,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1867,7 +1894,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2116,352 +2143,458 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="57">
-        <v>0.4327959493670886</v>
-      </c>
-      <c r="D16" s="57">
-        <v>0.3271641653940222</v>
-      </c>
-      <c r="E16" s="57">
-        <v>0.26006523141330673</v>
-      </c>
-      <c r="F16" s="57">
-        <v>0.21945084145261293</v>
-      </c>
-      <c r="G16" s="57">
-        <v>0.1977265787647467</v>
-      </c>
-      <c r="H16" s="59" t="s">
+      <c r="C16" s="60">
+        <v>11602.36393166008</v>
+      </c>
+      <c r="D16" s="60">
+        <v>9225.218408969291</v>
+      </c>
+      <c r="E16" s="60">
+        <v>7752.739957287549</v>
+      </c>
+      <c r="F16" s="60">
+        <v>6909.958881978421</v>
+      </c>
+      <c r="G16" s="60">
+        <v>6533.71696583004</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="55" t="s">
+      <c r="C17" s="54">
+        <v>600</v>
+      </c>
+      <c r="D17" s="54">
+        <v>618</v>
+      </c>
+      <c r="E17" s="54">
+        <v>637</v>
+      </c>
+      <c r="F17" s="54">
+        <v>656</v>
+      </c>
+      <c r="G17" s="54">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="57">
-        <v>0.0690632911392405</v>
-      </c>
-      <c r="D17" s="57">
-        <v>0.053773342978638713</v>
-      </c>
-      <c r="E17" s="57">
-        <v>0.04402688361790943</v>
-      </c>
-      <c r="F17" s="57">
-        <v>0.038265273616513266</v>
-      </c>
-      <c r="G17" s="57">
-        <v>0.0355105016470044</v>
-      </c>
-      <c r="H17" s="59" t="s">
+      <c r="C18" s="58">
+        <v>1364</v>
+      </c>
+      <c r="D18" s="58">
+        <v>1080.7076923076922</v>
+      </c>
+      <c r="E18" s="58">
+        <v>904.4112499999999</v>
+      </c>
+      <c r="F18" s="58">
+        <v>805.6494810810811</v>
+      </c>
+      <c r="G18" s="58">
+        <v>767.5594931</v>
+      </c>
+      <c r="H18" s="59" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="55" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="55" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="57">
-        <v>0.42978632911392406</v>
-      </c>
-      <c r="D18" s="57">
-        <v>0.5540140928628567</v>
-      </c>
-      <c r="E18" s="57">
-        <v>0.6329595102775986</v>
-      </c>
-      <c r="F18" s="57">
-        <v>0.6805489018112733</v>
-      </c>
-      <c r="G18" s="57">
-        <v>0.7056028221142725</v>
-      </c>
-      <c r="H18" s="59" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="60">
-        <v>4</v>
-      </c>
-      <c r="D19" s="60">
-        <v>4</v>
-      </c>
-      <c r="E19" s="60">
-        <v>4</v>
-      </c>
-      <c r="F19" s="60">
-        <v>4</v>
-      </c>
-      <c r="G19" s="60">
-        <v>4</v>
-      </c>
-      <c r="H19" s="59" t="s">
-        <v>195</v>
+      <c r="C19" s="61">
+        <v>7897.64</v>
+      </c>
+      <c r="D19" s="61">
+        <v>10795.323076923078</v>
+      </c>
+      <c r="E19" s="61">
+        <v>12727.0125</v>
+      </c>
+      <c r="F19" s="61">
+        <v>14117.340540540541</v>
+      </c>
+      <c r="G19" s="61">
+        <v>15056.285</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="61">
-        <v>24.918336160088252</v>
-      </c>
-      <c r="D20" s="61">
-        <v>42.49175944353473</v>
-      </c>
-      <c r="E20" s="61">
-        <v>61.07215795277884</v>
-      </c>
-      <c r="F20" s="61">
-        <v>77.81650437986194</v>
-      </c>
-      <c r="G20" s="61">
-        <v>89.54573137806075</v>
+        <v>193</v>
+      </c>
+      <c r="C20" s="57">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D20" s="57">
+        <v>0.3271641653940222</v>
+      </c>
+      <c r="E20" s="57">
+        <v>0.26006523141330673</v>
+      </c>
+      <c r="F20" s="57">
+        <v>0.21945084145261293</v>
+      </c>
+      <c r="G20" s="57">
+        <v>0.1977265787647467</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="57">
+        <v>0.0690632911392405</v>
+      </c>
+      <c r="D21" s="57">
+        <v>0.053773342978638713</v>
+      </c>
+      <c r="E21" s="57">
+        <v>0.04402688361790943</v>
+      </c>
+      <c r="F21" s="57">
+        <v>0.038265273616513266</v>
+      </c>
+      <c r="G21" s="57">
+        <v>0.0355105016470044</v>
+      </c>
+      <c r="H21" s="59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="57">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D22" s="57">
+        <v>0.5540140928628567</v>
+      </c>
+      <c r="E22" s="57">
+        <v>0.6329595102775986</v>
+      </c>
+      <c r="F22" s="57">
+        <v>0.6805489018112733</v>
+      </c>
+      <c r="G22" s="57">
+        <v>0.7056028221142725</v>
+      </c>
+      <c r="H22" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="C21" s="40" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="62">
+        <v>4</v>
+      </c>
+      <c r="D23" s="62">
+        <v>4</v>
+      </c>
+      <c r="E23" s="62">
+        <v>4</v>
+      </c>
+      <c r="F23" s="62">
+        <v>4</v>
+      </c>
+      <c r="G23" s="62">
+        <v>4</v>
+      </c>
+      <c r="H23" s="59" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="63">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D24" s="63">
+        <v>42.49175944353473</v>
+      </c>
+      <c r="E24" s="63">
+        <v>61.07215795277884</v>
+      </c>
+      <c r="F24" s="63">
+        <v>77.81650437986194</v>
+      </c>
+      <c r="G24" s="63">
+        <v>89.54573137806075</v>
+      </c>
+      <c r="H24" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="62" t="str">
+      <c r="D25" s="64" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="62" t="str">
+      <c r="E25" s="64" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="62" t="str">
+      <c r="F25" s="64" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="62" t="str">
+      <c r="G25" s="64" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="59" t="s">
+      <c r="H25" s="59" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="55" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="63">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" s="65">
         <v>9</v>
       </c>
-      <c r="D22" s="64">
+      <c r="D26" s="66">
         <v>23</v>
       </c>
-      <c r="E22" s="60">
+      <c r="E26" s="62">
         <v>42</v>
       </c>
-      <c r="F22" s="65" t="s">
-        <v>200</v>
-      </c>
-      <c r="G22" s="65" t="s">
-        <v>200</v>
-      </c>
-      <c r="H22" s="59" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="F26" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="66" t="s">
+      <c r="G26" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="H26" s="59" t="s">
         <v>206</v>
       </c>
-      <c r="C25" s="40" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="C27" s="62">
+        <v>272</v>
+      </c>
+      <c r="D27" s="62">
+        <v>690</v>
+      </c>
+      <c r="E27" s="62">
+        <v>1267</v>
+      </c>
+      <c r="F27" s="62">
+        <v>1975</v>
+      </c>
+      <c r="G27" s="62">
+        <v>2773</v>
+      </c>
+      <c r="H27" s="59" t="s">
         <v>208</v>
       </c>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="66" t="s">
+      <c r="C29" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C26" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D26" s="67" t="s">
+      <c r="D29" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="66" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C27" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D27" s="67" t="s">
+      <c r="C30" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68" t="s">
+      <c r="D30" s="69" t="s">
         <v>215</v>
       </c>
-      <c r="G27" s="68"/>
-      <c r="H27" s="68"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="66" t="s">
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D28" s="67" t="s">
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68" t="s">
+      <c r="C31" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D31" s="69" t="s">
         <v>218</v>
       </c>
-      <c r="G28" s="68"/>
-      <c r="H28" s="68"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="66" t="s">
+      <c r="E31" s="69"/>
+      <c r="F31" s="70" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D29" s="67" t="s">
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68" t="s">
+      <c r="C32" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
+      <c r="E32" s="69"/>
+      <c r="F32" s="70" t="s">
         <v>222</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D30" s="67" t="s">
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68" t="s">
+      <c r="C33" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D33" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
+      <c r="E33" s="69"/>
+      <c r="F33" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D31" s="67" t="s">
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="67"/>
-      <c r="F31" s="68" t="s">
+      <c r="C34" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D34" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+      <c r="E34" s="69"/>
+      <c r="F34" s="70" t="s">
+        <v>228</v>
+      </c>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="68" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>230</v>
+      </c>
+      <c r="E35" s="69"/>
+      <c r="F35" s="70" t="s">
+        <v>231</v>
+      </c>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="69" t="s">
+        <v>233</v>
+      </c>
+      <c r="E36" s="69"/>
+      <c r="F36" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="55" t="s">
-        <v>228</v>
-      </c>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="69" t="s">
-        <v>229</v>
-      </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
+      <c r="C38" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="71" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2507,48 +2640,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -16,7 +16,7 @@
     <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Prior-Year Snapshot'!$A1:$B9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="238">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -174,6 +174,9 @@
     <t>July</t>
   </si>
   <si>
+    <t>Accounting Basis</t>
+  </si>
+  <si>
     <t>Accredited</t>
   </si>
   <si>
@@ -567,7 +570,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1630,7 +1633,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1748,69 +1751,69 @@
         <v>44</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>52</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="23" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="B20" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="24">
-        <v>100</v>
-      </c>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="24">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1818,7 +1821,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="24">
-        <v>160</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1826,7 +1829,7 @@
         <v>60</v>
       </c>
       <c r="B25" s="24">
-        <v>185</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1834,22 +1837,22 @@
         <v>61</v>
       </c>
       <c r="B26" s="24">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="24">
         <v>200</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="25">
-        <v>0</v>
-      </c>
+      <c r="B29" s="8"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
@@ -1863,16 +1866,24 @@
       <c r="A31" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="26">
-        <v>1</v>
+      <c r="B31" s="25">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
         <v>67</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1906,7 +1917,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
@@ -1917,7 +1928,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -1928,41 +1939,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F4" s="51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" s="53">
         <v>100</v>
@@ -1982,7 +1993,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C8" s="54">
         <v>1975000</v>
@@ -2002,7 +2013,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C9" s="54">
         <v>854772</v>
@@ -2042,7 +2053,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C11" s="54">
         <v>34064.39316600799</v>
@@ -2062,7 +2073,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="55" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="56">
         <v>789764</v>
@@ -2082,7 +2093,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C13" s="56">
         <v>864764</v>
@@ -2102,7 +2113,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C14" s="57">
         <v>0.3998805063291139</v>
@@ -2122,7 +2133,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="58">
         <v>19750</v>
@@ -2140,12 +2151,12 @@
         <v>21615</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="60">
         <v>11602.36393166008</v>
@@ -2165,7 +2176,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C17" s="54">
         <v>600</v>
@@ -2185,7 +2196,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="58">
         <v>1364</v>
@@ -2203,12 +2214,12 @@
         <v>767.5594931</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C19" s="61">
         <v>7897.64</v>
@@ -2228,7 +2239,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" s="57">
         <v>0.4327959493670886</v>
@@ -2246,12 +2257,12 @@
         <v>0.1977265787647467</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C21" s="57">
         <v>0.0690632911392405</v>
@@ -2269,12 +2280,12 @@
         <v>0.0355105016470044</v>
       </c>
       <c r="H21" s="59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C22" s="57">
         <v>0.42978632911392406</v>
@@ -2292,12 +2303,12 @@
         <v>0.7056028221142725</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C23" s="62">
         <v>4</v>
@@ -2315,12 +2326,12 @@
         <v>4</v>
       </c>
       <c r="H23" s="59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C24" s="63">
         <v>24.918336160088252</v>
@@ -2338,12 +2349,12 @@
         <v>89.54573137806075</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C25" s="40" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
@@ -2366,12 +2377,12 @@
         <v>0</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C26" s="65">
         <v>9</v>
@@ -2383,18 +2394,18 @@
         <v>42</v>
       </c>
       <c r="F26" s="67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G26" s="67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="55" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C27" s="62">
         <v>272</v>
@@ -2412,141 +2423,141 @@
         <v>2773</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D30" s="69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E30" s="69"/>
       <c r="F30" s="70" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G30" s="70"/>
       <c r="H30" s="70"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D31" s="69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E31" s="69"/>
       <c r="F31" s="70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G31" s="70"/>
       <c r="H31" s="70"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D32" s="69" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E32" s="69"/>
       <c r="F32" s="70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G32" s="70"/>
       <c r="H32" s="70"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D33" s="69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E33" s="69"/>
       <c r="F33" s="70" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G33" s="70"/>
       <c r="H33" s="70"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D34" s="69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E34" s="69"/>
       <c r="F34" s="70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="68" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D35" s="69" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E35" s="69"/>
       <c r="F35" s="70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G35" s="70"/>
       <c r="H35" s="70"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D36" s="69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E36" s="69"/>
       <c r="F36" s="70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G36" s="70"/>
       <c r="H36" s="70"/>
@@ -2556,7 +2567,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D38" s="55"/>
       <c r="E38" s="55"/>
@@ -2564,7 +2575,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="71" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C40" s="71"/>
       <c r="D40" s="71"/>
@@ -2678,10 +2689,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2710,49 +2721,49 @@
         <v>24</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>100</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>130</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>160</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>185</v>
       </c>
       <c r="F2" s="29">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2762,57 +2773,57 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="30">
-        <f>10500*Assumptions!B22</f>
+        <f>10500*Assumptions!B23</f>
         <v>1050000</v>
       </c>
       <c r="C4" s="30">
-        <f>10815*Assumptions!B23</f>
+        <f>10815*Assumptions!B24</f>
         <v>1405950</v>
       </c>
       <c r="D4" s="30">
-        <f>11140*Assumptions!B24</f>
+        <f>11140*Assumptions!B25</f>
         <v>1782400</v>
       </c>
       <c r="E4" s="30">
-        <f>11474*Assumptions!B25</f>
+        <f>11474*Assumptions!B26</f>
         <v>2122690</v>
       </c>
       <c r="F4" s="30">
-        <f>11818*Assumptions!B26</f>
+        <f>11818*Assumptions!B27</f>
         <v>2363600</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="30">
-        <f>350*Assumptions!B22</f>
+        <f>350*Assumptions!B23</f>
         <v>35000</v>
       </c>
       <c r="C5" s="30">
-        <f>350*Assumptions!B23</f>
+        <f>350*Assumptions!B24</f>
         <v>45500</v>
       </c>
       <c r="D5" s="30">
-        <f>350*Assumptions!B24</f>
+        <f>350*Assumptions!B25</f>
         <v>56000</v>
       </c>
       <c r="E5" s="30">
-        <f>350*Assumptions!B25</f>
+        <f>350*Assumptions!B26</f>
         <v>64750</v>
       </c>
       <c r="F5" s="30">
-        <f>350*Assumptions!B26</f>
+        <f>350*Assumptions!B27</f>
         <v>70000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B4:B5)</f>
@@ -2837,7 +2848,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2847,32 +2858,32 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="30">
-        <f>--1050*Assumptions!B22</f>
+        <f>--1050*Assumptions!B23</f>
         <v>-105000</v>
       </c>
       <c r="C8" s="30">
-        <f>--1082*Assumptions!B23</f>
+        <f>--1082*Assumptions!B24</f>
         <v>-140660</v>
       </c>
       <c r="D8" s="30">
-        <f>--1114*Assumptions!B24</f>
+        <f>--1114*Assumptions!B25</f>
         <v>-178240</v>
       </c>
       <c r="E8" s="30">
-        <f>--1147*Assumptions!B25</f>
+        <f>--1147*Assumptions!B26</f>
         <v>-212195</v>
       </c>
       <c r="F8" s="30">
-        <f>--1182*Assumptions!B26</f>
+        <f>--1182*Assumptions!B27</f>
         <v>-236400</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -2897,7 +2908,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2907,32 +2918,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="30">
-        <f>8700*Assumptions!B22</f>
+        <f>8700*Assumptions!B23</f>
         <v>870000</v>
       </c>
       <c r="C11" s="30">
-        <f>8961*Assumptions!B23</f>
+        <f>8961*Assumptions!B24</f>
         <v>1164930</v>
       </c>
       <c r="D11" s="30">
-        <f>9230*Assumptions!B24</f>
+        <f>9230*Assumptions!B25</f>
         <v>1476800</v>
       </c>
       <c r="E11" s="30">
-        <f>9507*Assumptions!B25</f>
+        <f>9507*Assumptions!B26</f>
         <v>1758795</v>
       </c>
       <c r="F11" s="30">
-        <f>9792*Assumptions!B26</f>
+        <f>9792*Assumptions!B27</f>
         <v>1958400</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B11:B11)</f>
@@ -2957,7 +2968,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2967,7 +2978,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="30">
         <v>50000</v>
@@ -2987,7 +2998,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="30">
         <v>25000</v>
@@ -3007,7 +3018,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B14:B15)</f>
@@ -3032,7 +3043,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -3042,32 +3053,32 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" s="30">
-        <f>500*Assumptions!B22</f>
+        <f>500*Assumptions!B23</f>
         <v>50000</v>
       </c>
       <c r="C18" s="30">
-        <f>515*Assumptions!B23</f>
+        <f>515*Assumptions!B24</f>
         <v>66950</v>
       </c>
       <c r="D18" s="30">
-        <f>530*Assumptions!B24</f>
+        <f>530*Assumptions!B25</f>
         <v>84800</v>
       </c>
       <c r="E18" s="30">
-        <f>546*Assumptions!B25</f>
+        <f>546*Assumptions!B26</f>
         <v>101010</v>
       </c>
       <c r="F18" s="30">
-        <f>562*Assumptions!B26</f>
+        <f>562*Assumptions!B27</f>
         <v>112400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B18:B18)</f>
@@ -3092,7 +3103,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B21" s="31">
         <f>B6+B9+B12+B16+B19</f>
@@ -3139,7 +3150,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3151,39 +3162,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D4" s="26">
         <v>1</v>
@@ -3203,13 +3214,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>104</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>103</v>
       </c>
       <c r="D5" s="26">
         <v>1</v>
@@ -3229,13 +3240,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" s="26">
         <v>6</v>
@@ -3255,13 +3266,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>106</v>
-      </c>
       <c r="C7" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D7" s="26">
         <v>3</v>
@@ -3281,13 +3292,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -3307,13 +3318,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" s="26">
         <v>1</v>
@@ -3333,7 +3344,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3345,7 +3356,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" s="34">
         <v>6</v>
@@ -3353,7 +3364,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B13" s="34">
         <v>13</v>
@@ -3361,7 +3372,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B14" s="35">
         <v>648000</v>
@@ -3369,7 +3380,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="35">
         <v>157200</v>
@@ -3377,7 +3388,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="35">
         <v>49572</v>
@@ -3385,7 +3396,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B17" s="35">
         <v>0</v>
@@ -3393,7 +3404,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="36">
         <v>854772</v>
@@ -3401,7 +3412,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -3414,24 +3425,24 @@
         <v>24</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B22" s="30">
         <v>854772</v>
@@ -3451,35 +3462,35 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B23" s="37">
-        <f>(1+Assumptions!B29)^0</f>
+        <f>(1+Assumptions!B30)^0</f>
         <v>1</v>
       </c>
       <c r="C23" s="37">
-        <f>(1+Assumptions!B29)^1</f>
+        <f>(1+Assumptions!B30)^1</f>
         <v>1</v>
       </c>
       <c r="D23" s="37">
-        <f>(1+Assumptions!B29)^2</f>
+        <f>(1+Assumptions!B30)^2</f>
         <v>1</v>
       </c>
       <c r="E23" s="37">
-        <f>(1+Assumptions!B29)^3</f>
+        <f>(1+Assumptions!B30)^3</f>
         <v>1</v>
       </c>
       <c r="F23" s="37">
-        <f>(1+Assumptions!B29)^4</f>
+        <f>(1+Assumptions!B30)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B24" s="38">
-        <f>Assumptions!B31</f>
+        <f>Assumptions!B32</f>
         <v>1</v>
       </c>
       <c r="C24" s="38">
@@ -3497,7 +3508,7 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B25" s="31">
         <f>B22*B23*B24</f>
@@ -3550,49 +3561,49 @@
         <v>24</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>100</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>130</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>160</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>185</v>
       </c>
       <c r="F2" s="29">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3602,32 +3613,32 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="30">
-        <f>600*Assumptions!B22</f>
+        <f>600*Assumptions!B23</f>
         <v>60000</v>
       </c>
       <c r="C4" s="30">
-        <f>618*Assumptions!B23</f>
+        <f>618*Assumptions!B24</f>
         <v>80340</v>
       </c>
       <c r="D4" s="30">
-        <f>637*Assumptions!B24</f>
+        <f>637*Assumptions!B25</f>
         <v>101920</v>
       </c>
       <c r="E4" s="30">
-        <f>656*Assumptions!B25</f>
+        <f>656*Assumptions!B26</f>
         <v>121360</v>
       </c>
       <c r="F4" s="30">
-        <f>675*Assumptions!B26</f>
+        <f>675*Assumptions!B27</f>
         <v>135000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -3652,7 +3663,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3662,32 +3673,32 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B7" s="30">
-        <f>400*Assumptions!B22</f>
+        <f>400*Assumptions!B23</f>
         <v>40000</v>
       </c>
       <c r="C7" s="30">
-        <f>412*Assumptions!B23</f>
+        <f>412*Assumptions!B24</f>
         <v>53560</v>
       </c>
       <c r="D7" s="30">
-        <f>424*Assumptions!B24</f>
+        <f>424*Assumptions!B25</f>
         <v>67840</v>
       </c>
       <c r="E7" s="30">
-        <f>437*Assumptions!B25</f>
+        <f>437*Assumptions!B26</f>
         <v>80845</v>
       </c>
       <c r="F7" s="30">
-        <f>450*Assumptions!B26</f>
+        <f>450*Assumptions!B27</f>
         <v>90000</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -3712,7 +3723,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3722,7 +3733,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B10" s="30">
         <f>8500*12</f>
@@ -3747,7 +3758,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" s="30">
         <f>1200*12</f>
@@ -3772,7 +3783,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B12" s="30">
         <v>12000</v>
@@ -3792,7 +3803,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B13" s="30">
         <v>8000</v>
@@ -3812,7 +3823,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B10:B13)</f>
@@ -3837,7 +3848,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -3847,7 +3858,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B16" s="30">
         <v>15000</v>
@@ -3867,7 +3878,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B17" s="30">
         <v>8000</v>
@@ -3887,7 +3898,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" s="30">
         <v>12000</v>
@@ -3907,7 +3918,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B16:B18)</f>
@@ -3932,7 +3943,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="31">
         <f>B5+B8+B14+B19</f>
@@ -3982,24 +3993,24 @@
         <v>24</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4009,7 +4020,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B3" s="30">
         <v>34064.39316600799</v>
@@ -4029,7 +4040,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="30">
         <v>25000</v>
@@ -4049,7 +4060,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B3:B4)</f>
@@ -4099,24 +4110,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B21</f>
@@ -4141,7 +4152,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B25</f>
@@ -4216,7 +4227,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -4241,7 +4252,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -4266,7 +4277,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -4316,10 +4327,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>24</v>
@@ -4349,7 +4360,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -4358,7 +4369,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -4368,7 +4379,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,134 +4450,117 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="28" t="s">
+      <c r="B16" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="C16" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="D16" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="E16" s="28" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="F16" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="29">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>100</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>130</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D17" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>160</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E17" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>185</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F17" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="9" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="44">
-        <f>IF(B16=0,0,(C16-B16)/B16)</f>
+      <c r="B18" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="44">
+        <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.3</v>
       </c>
-      <c r="D17" s="44">
-        <f>IF(C16=0,0,(D16-C16)/C16)</f>
+      <c r="D18" s="44">
+        <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="E17" s="44">
-        <f>IF(D16=0,0,(E16-D16)/D16)</f>
+      <c r="E18" s="44">
+        <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.15625</v>
       </c>
-      <c r="F17" s="44">
-        <f>IF(E16=0,0,(F16-E16)/E16)</f>
+      <c r="F18" s="44">
+        <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.08108108108108109</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="28" t="s">
+      <c r="B20" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="C20" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="D20" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="E20" s="28" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="30">
-        <f>'Financial Model'!B2</f>
-        <v>1975000</v>
-      </c>
-      <c r="C20" s="30">
-        <f>'Financial Model'!C2</f>
-        <v>2612670</v>
-      </c>
-      <c r="D20" s="30">
-        <f>'Financial Model'!D2</f>
-        <v>3286760</v>
-      </c>
-      <c r="E20" s="30">
-        <f>'Financial Model'!E2</f>
-        <v>3895050</v>
-      </c>
-      <c r="F20" s="30">
-        <f>'Financial Model'!F2</f>
-        <v>4323000</v>
+      <c r="F20" s="28" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4574,209 +4568,209 @@
         <v>148</v>
       </c>
       <c r="B21" s="30">
+        <f>'Financial Model'!B2</f>
+        <v>1975000</v>
+      </c>
+      <c r="C21" s="30">
+        <f>'Financial Model'!C2</f>
+        <v>2612670</v>
+      </c>
+      <c r="D21" s="30">
+        <f>'Financial Model'!D2</f>
+        <v>3286760</v>
+      </c>
+      <c r="E21" s="30">
+        <f>'Financial Model'!E2</f>
+        <v>3895050</v>
+      </c>
+      <c r="F21" s="30">
+        <f>'Financial Model'!F2</f>
+        <v>4323000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="30">
         <f>'Financial Model'!C3</f>
         <v>854772</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D22" s="30">
         <f>'Financial Model'!D3</f>
         <v>854772</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E22" s="30">
         <f>'Financial Model'!E3</f>
         <v>854772</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F22" s="30">
         <f>'Financial Model'!F3</f>
         <v>854772</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B23" s="30">
         <f>'Financial Model'!B4</f>
         <v>271400</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="30">
         <f>'Financial Model'!C4</f>
         <v>310442</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D23" s="30">
         <f>'Financial Model'!D4</f>
         <v>351602</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E23" s="30">
         <f>'Financial Model'!E4</f>
         <v>389506</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F23" s="30">
         <f>'Financial Model'!F4</f>
         <v>417907</v>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="31">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
         <v>1185236</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f>'Financial Model'!C6</f>
         <v>1209278</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D24" s="31">
         <f>'Financial Model'!D6</f>
         <v>1250438</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E24" s="31">
         <f>'Financial Model'!E6</f>
         <v>1283342</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F24" s="31">
         <f>'Financial Model'!F6</f>
         <v>1311743</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="B24" s="45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="45">
         <f>'Financial Model'!B7</f>
         <v>789764</v>
       </c>
-      <c r="C24" s="45">
+      <c r="C25" s="45">
         <f>'Financial Model'!C7</f>
         <v>1403392</v>
       </c>
-      <c r="D24" s="45">
+      <c r="D25" s="45">
         <f>'Financial Model'!D7</f>
         <v>2036322</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E25" s="45">
         <f>'Financial Model'!E7</f>
         <v>2611708</v>
       </c>
-      <c r="F24" s="45">
+      <c r="F25" s="45">
         <f>'Financial Model'!F7</f>
         <v>3011257</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="30">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
         <v>789764</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="30">
         <f>'Financial Model'!C8</f>
         <v>2193156</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D26" s="30">
         <f>'Financial Model'!D8</f>
         <v>4229478</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E26" s="30">
         <f>'Financial Model'!E8</f>
         <v>6841186</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F26" s="30">
         <f>'Financial Model'!F8</f>
         <v>9852443</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B27" s="13">
         <f>'Financial Model'!B9</f>
         <v>7.996017670742367</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C27" s="13">
         <f>'Financial Model'!C9</f>
         <v>21.763293469326324</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D27" s="13">
         <f>'Financial Model'!D9</f>
         <v>40.58876649621972</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E27" s="13">
         <f>'Financial Model'!E9</f>
         <v>63.969099429458396</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F27" s="13">
         <f>'Financial Model'!F9</f>
         <v>90.1314632515668</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="30">
-        <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
-        <v>19750</v>
-      </c>
-      <c r="C29" s="30">
-        <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
-        <v>20097.46153846154</v>
-      </c>
-      <c r="D29" s="30">
-        <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
-        <v>20542.25</v>
-      </c>
-      <c r="E29" s="30">
-        <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
-        <v>21054.324324324323</v>
-      </c>
-      <c r="F29" s="30">
-        <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
-        <v>21615</v>
-      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B30" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
-        <v>0.4327959493670886</v>
-      </c>
-      <c r="C30" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
-        <v>0.3271641653940222</v>
-      </c>
-      <c r="D30" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
-        <v>0.26006523141330673</v>
-      </c>
-      <c r="E30" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
-        <v>0.21945084145261293</v>
-      </c>
-      <c r="F30" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
-        <v>0.1977265787647467</v>
+      <c r="B30" s="30">
+        <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
+        <v>19750</v>
+      </c>
+      <c r="C30" s="30">
+        <f>IF('Revenue Schedule'!C2=0,0,C21/'Revenue Schedule'!C2)</f>
+        <v>20097.46153846154</v>
+      </c>
+      <c r="D30" s="30">
+        <f>IF('Revenue Schedule'!D2=0,0,D21/'Revenue Schedule'!D2)</f>
+        <v>20542.25</v>
+      </c>
+      <c r="E30" s="30">
+        <f>IF('Revenue Schedule'!E2=0,0,E21/'Revenue Schedule'!E2)</f>
+        <v>21054.324324324323</v>
+      </c>
+      <c r="F30" s="30">
+        <f>IF('Revenue Schedule'!F2=0,0,F21/'Revenue Schedule'!F2)</f>
+        <v>21615</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4784,99 +4778,104 @@
         <v>163</v>
       </c>
       <c r="B31" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
+        <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="C31" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
+        <v>0.3271641653940222</v>
+      </c>
+      <c r="D31" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
+        <v>0.26006523141330673</v>
+      </c>
+      <c r="E31" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
+        <v>0.21945084145261293</v>
+      </c>
+      <c r="F31" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
+        <v>0.1977265787647467</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="44">
+        <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.13741772151898735</v>
       </c>
-      <c r="C31" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
+      <c r="C32" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.11882174174312102</v>
       </c>
-      <c r="D31" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
+      <c r="D32" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.10697525830909467</v>
       </c>
-      <c r="E31" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
+      <c r="E32" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.10000025673611379</v>
       </c>
-      <c r="F31" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
+      <c r="F32" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.0966705991209808</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" s="12">
-        <f>IF(B20=0,0,B24/B20)</f>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="12">
+        <f>IF(B21=0,0,B25/B21)</f>
         <v>0.3998805063291139</v>
       </c>
-      <c r="C32" s="12">
-        <f>IF(C20=0,0,C24/C20)</f>
+      <c r="C33" s="12">
+        <f>IF(C21=0,0,C25/C21)</f>
         <v>0.5371485874603376</v>
       </c>
-      <c r="D32" s="12">
-        <f>IF(D20=0,0,D24/D20)</f>
+      <c r="D33" s="12">
+        <f>IF(D21=0,0,D25/D21)</f>
         <v>0.6195529944382918</v>
       </c>
-      <c r="E32" s="12">
-        <f>IF(E20=0,0,E24/E20)</f>
+      <c r="E33" s="12">
+        <f>IF(E21=0,0,E25/E21)</f>
         <v>0.6705197622623587</v>
       </c>
-      <c r="F32" s="12">
-        <f>IF(F20=0,0,F24/F20)</f>
+      <c r="F33" s="12">
+        <f>IF(F21=0,0,F25/F21)</f>
         <v>0.6965665047420773</v>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="44">
-        <v>0.5675057208237986</v>
-      </c>
-      <c r="C35" s="44">
-        <v>0.5732777238345675</v>
-      </c>
-      <c r="D35" s="44">
-        <v>0.5768052612509744</v>
-      </c>
-      <c r="E35" s="44">
-        <v>0.5789280554886744</v>
-      </c>
-      <c r="F35" s="44">
-        <v>0.5801743191959632</v>
-      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
         <v>167</v>
       </c>
       <c r="B36" s="44">
-        <v>0.39816933638443935</v>
+        <v>0.5675057208237986</v>
       </c>
       <c r="C36" s="44">
-        <v>0.4025342174644695</v>
+        <v>0.5732777238345675</v>
       </c>
       <c r="D36" s="44">
-        <v>0.4053534765757952</v>
+        <v>0.5768052612509744</v>
       </c>
       <c r="E36" s="44">
-        <v>0.4071812549774971</v>
+        <v>0.5789280554886744</v>
       </c>
       <c r="F36" s="44">
-        <v>0.4083573126485675</v>
+        <v>0.5801743191959632</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4884,18 +4883,38 @@
         <v>168</v>
       </c>
       <c r="B37" s="44">
+        <v>0.39816933638443935</v>
+      </c>
+      <c r="C37" s="44">
+        <v>0.4025342174644695</v>
+      </c>
+      <c r="D37" s="44">
+        <v>0.4053534765757952</v>
+      </c>
+      <c r="E37" s="44">
+        <v>0.4071812549774971</v>
+      </c>
+      <c r="F37" s="44">
+        <v>0.4083573126485675</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B38" s="44">
         <v>0.034324942791762014</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C38" s="44">
         <v>0.02418805870096303</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D38" s="44">
         <v>0.01784126217323042</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E38" s="44">
         <v>0.01389068953382846</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F38" s="44">
         <v>0.01146836815546937</v>
       </c>
     </row>
@@ -4932,13 +4951,13 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B4" s="46">
         <v>85</v>
@@ -4946,7 +4965,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="36">
         <v>1200000</v>
@@ -4954,7 +4973,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="36">
         <v>1150000</v>
@@ -4962,7 +4981,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B7" s="36">
         <v>75000</v>
@@ -4970,7 +4989,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B8" s="36">
         <v>50000</v>
@@ -4978,7 +4997,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B9" s="47">
         <v>0.8</v>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="9" name="Cover" state="visible" r:id="rId4"/>
+    <sheet sheetId="10" name="Cover" state="visible" r:id="rId4"/>
     <sheet sheetId="1" name="Assumptions" state="visible" r:id="rId5"/>
     <sheet sheetId="2" name="Revenue Schedule" state="visible" r:id="rId6"/>
     <sheet sheetId="3" name="Staffing &amp; Personnel" state="visible" r:id="rId7"/>
@@ -13,7 +13,8 @@
     <sheet sheetId="6" name="Financial Model" state="visible" r:id="rId10"/>
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
     <sheet sheetId="8" name="Prior-Year Snapshot" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
+    <sheet sheetId="9" name="Decision History" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E33</definedName>
@@ -32,15 +33,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Prior-Year Snapshot'!$A1:$B9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Decision History'!$A1:$H4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Decision History'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="241">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -108,6 +111,9 @@
     <t>Prior-Year Snapshot</t>
   </si>
   <si>
+    <t>Decision History</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
@@ -565,6 +571,12 @@
   </si>
   <si>
     <t>Cash Reserve (Months)</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
   <si>
     <t>Heritage Academy — Financial Health Dashboard</t>
@@ -769,7 +781,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -882,6 +894,12 @@
       <i/>
       <color rgb="FF6B7280"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1009,7 +1027,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1064,10 +1082,16 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1642,33 +1666,33 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>3</v>
@@ -1676,47 +1700,47 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="23">
         <v>2023</v>
@@ -1724,7 +1748,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="23">
         <v>85</v>
@@ -1732,7 +1756,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="23">
         <v>200</v>
@@ -1740,77 +1764,77 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="8"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="24">
         <v>100</v>
@@ -1818,7 +1842,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="24">
         <v>130</v>
@@ -1826,7 +1850,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="24">
         <v>160</v>
@@ -1834,7 +1858,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="24">
         <v>185</v>
@@ -1842,7 +1866,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="24">
         <v>200</v>
@@ -1850,13 +1874,13 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="8"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="25">
         <v>0</v>
@@ -1864,7 +1888,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B31" s="25">
         <v>0</v>
@@ -1872,7 +1896,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" s="26">
         <v>1</v>
@@ -1880,10 +1904,10 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1900,6 +1924,199 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:C35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="10">
+        <v>4323000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="11">
+        <v>3011257</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0.6965665047420773</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="13">
+        <v>90.1314632515668</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="16"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B35:C35"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B24" r:id="rId1" location="#'Assumptions'!A1"/>
+    <hyperlink ref="B25" r:id="rId2" location="#'Revenue Schedule'!A1"/>
+    <hyperlink ref="B26" r:id="rId3" location="#'Staffing &amp; Personnel'!A1"/>
+    <hyperlink ref="B27" r:id="rId4" location="#'Operating Expenses'!A1"/>
+    <hyperlink ref="B28" r:id="rId5" location="#'Capital &amp; Debt'!A1"/>
+    <hyperlink ref="B29" r:id="rId6" location="#'Financial Model'!A1"/>
+    <hyperlink ref="B30" r:id="rId7" location="#'Summary'!A1"/>
+    <hyperlink ref="B31" r:id="rId8" location="#'Prior-Year Snapshot'!A1"/>
+    <hyperlink ref="B32" r:id="rId9" location="#'Decision History'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -1917,7 +2134,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
@@ -1927,107 +2144,107 @@
       <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
+      <c r="B3" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>179</v>
+      <c r="B4" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="D6" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="E6" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="F6" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="52" t="s">
-        <v>181</v>
+      <c r="G6" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="54" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="53">
+        <v>185</v>
+      </c>
+      <c r="C7" s="55">
         <v>100</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="55">
         <v>130</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="55">
         <v>160</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="55">
         <v>185</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="55">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="54">
+        <v>186</v>
+      </c>
+      <c r="C8" s="56">
         <v>1975000</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="56">
         <v>2612670</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="56">
         <v>3286760</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="56">
         <v>3895050</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="56">
         <v>4323000</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C9" s="54">
+        <v>187</v>
+      </c>
+      <c r="C9" s="56">
         <v>854772</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="56">
         <v>854772</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="56">
         <v>854772</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="56">
         <v>854772</v>
       </c>
-      <c r="G9" s="54">
+      <c r="G9" s="56">
         <v>854772</v>
       </c>
     </row>
@@ -2035,554 +2252,554 @@
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="56">
         <v>271400</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="56">
         <v>310442</v>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="56">
         <v>351602</v>
       </c>
-      <c r="F10" s="54">
+      <c r="F10" s="56">
         <v>389506</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="56">
         <v>417907</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C11" s="54">
+        <v>188</v>
+      </c>
+      <c r="C11" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F11" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="56">
         <v>34064.39316600799</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="55" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="56">
+      <c r="B12" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="58">
         <v>789764</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="58">
         <v>1403392</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="58">
         <v>2036322</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="58">
         <v>2611708</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="58">
         <v>3011257</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="56">
+      <c r="B13" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="58">
         <v>864764</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="58">
         <v>2268156</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="58">
         <v>4304478</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="58">
         <v>6916186</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="58">
         <v>9927443</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="C14" s="57">
+      <c r="B14" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="59">
         <v>0.3998805063291139</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="59">
         <v>0.5371485874603376</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="59">
         <v>0.6195529944382918</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="59">
         <v>0.6705197622623587</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G14" s="59">
         <v>0.6965665047420773</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="58">
+      <c r="B15" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="60">
         <v>19750</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="60">
         <v>20097.46153846154</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E15" s="60">
         <v>20542.25</v>
       </c>
-      <c r="F15" s="58">
+      <c r="F15" s="60">
         <v>21054.324324324323</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G15" s="60">
         <v>21615</v>
       </c>
-      <c r="H15" s="59" t="s">
-        <v>188</v>
+      <c r="H15" s="61" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="C16" s="60">
+      <c r="B16" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="62">
         <v>11602.36393166008</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="62">
         <v>9225.218408969291</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E16" s="62">
         <v>7752.739957287549</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="62">
         <v>6909.958881978421</v>
       </c>
-      <c r="G16" s="60">
+      <c r="G16" s="62">
         <v>6533.71696583004</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C17" s="54">
+        <v>193</v>
+      </c>
+      <c r="C17" s="56">
         <v>600</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="56">
         <v>618</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="56">
         <v>637</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="56">
         <v>656</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="56">
         <v>675</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C18" s="58">
+        <v>194</v>
+      </c>
+      <c r="C18" s="60">
         <v>1364</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="60">
         <v>1080.7076923076922</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="60">
         <v>904.4112499999999</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="60">
         <v>805.6494810810811</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="60">
         <v>767.5594931</v>
       </c>
-      <c r="H18" s="59" t="s">
-        <v>192</v>
+      <c r="H18" s="61" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="C19" s="61">
+      <c r="B19" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="63">
         <v>7897.64</v>
       </c>
-      <c r="D19" s="61">
+      <c r="D19" s="63">
         <v>10795.323076923078</v>
       </c>
-      <c r="E19" s="61">
+      <c r="E19" s="63">
         <v>12727.0125</v>
       </c>
-      <c r="F19" s="61">
+      <c r="F19" s="63">
         <v>14117.340540540541</v>
       </c>
-      <c r="G19" s="61">
+      <c r="G19" s="63">
         <v>15056.285</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="55" t="s">
-        <v>194</v>
-      </c>
-      <c r="C20" s="57">
+      <c r="B20" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="59">
         <v>0.4327959493670886</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="59">
         <v>0.3271641653940222</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="59">
         <v>0.26006523141330673</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="59">
         <v>0.21945084145261293</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="59">
         <v>0.1977265787647467</v>
       </c>
-      <c r="H20" s="59" t="s">
-        <v>195</v>
+      <c r="H20" s="61" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="C21" s="57">
+      <c r="B21" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" s="59">
         <v>0.0690632911392405</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="59">
         <v>0.053773342978638713</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="59">
         <v>0.04402688361790943</v>
       </c>
-      <c r="F21" s="57">
+      <c r="F21" s="59">
         <v>0.038265273616513266</v>
       </c>
-      <c r="G21" s="57">
+      <c r="G21" s="59">
         <v>0.0355105016470044</v>
       </c>
-      <c r="H21" s="59" t="s">
-        <v>197</v>
+      <c r="H21" s="61" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="55" t="s">
-        <v>198</v>
-      </c>
-      <c r="C22" s="57">
+      <c r="B22" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="59">
         <v>0.42978632911392406</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D22" s="59">
         <v>0.5540140928628567</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22" s="59">
         <v>0.6329595102775986</v>
       </c>
-      <c r="F22" s="57">
+      <c r="F22" s="59">
         <v>0.6805489018112733</v>
       </c>
-      <c r="G22" s="57">
+      <c r="G22" s="59">
         <v>0.7056028221142725</v>
       </c>
-      <c r="H22" s="59" t="s">
-        <v>199</v>
+      <c r="H22" s="61" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" s="62">
+      <c r="B23" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="64">
         <v>4</v>
       </c>
-      <c r="D23" s="62">
+      <c r="D23" s="64">
         <v>4</v>
       </c>
-      <c r="E23" s="62">
+      <c r="E23" s="64">
         <v>4</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="64">
         <v>4</v>
       </c>
-      <c r="G23" s="62">
+      <c r="G23" s="64">
         <v>4</v>
       </c>
-      <c r="H23" s="59" t="s">
-        <v>201</v>
+      <c r="H23" s="61" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="55" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="63">
+      <c r="B24" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="C24" s="65">
         <v>24.918336160088252</v>
       </c>
-      <c r="D24" s="63">
+      <c r="D24" s="65">
         <v>42.49175944353473</v>
       </c>
-      <c r="E24" s="63">
+      <c r="E24" s="65">
         <v>61.07215795277884</v>
       </c>
-      <c r="F24" s="63">
+      <c r="F24" s="65">
         <v>77.81650437986194</v>
       </c>
-      <c r="G24" s="63">
+      <c r="G24" s="65">
         <v>89.54573137806075</v>
       </c>
-      <c r="H24" s="59" t="s">
-        <v>203</v>
+      <c r="H24" s="61" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
-        <v>204</v>
+      <c r="B25" s="57" t="s">
+        <v>207</v>
       </c>
       <c r="C25" s="40" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="64" t="str">
+      <c r="D25" s="66" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="64" t="str">
+      <c r="E25" s="66" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="64" t="str">
+      <c r="F25" s="66" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="64" t="str">
+      <c r="G25" s="66" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="59" t="s">
-        <v>69</v>
+      <c r="H25" s="61" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="55" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="65">
+      <c r="B26" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="67">
         <v>9</v>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="68">
         <v>23</v>
       </c>
-      <c r="E26" s="62">
+      <c r="E26" s="64">
         <v>42</v>
       </c>
-      <c r="F26" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="G26" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="H26" s="59" t="s">
-        <v>207</v>
+      <c r="F26" s="69" t="s">
+        <v>209</v>
+      </c>
+      <c r="G26" s="69" t="s">
+        <v>209</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
-        <v>208</v>
-      </c>
-      <c r="C27" s="62">
+      <c r="B27" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="C27" s="64">
         <v>272</v>
       </c>
-      <c r="D27" s="62">
+      <c r="D27" s="64">
         <v>690</v>
       </c>
-      <c r="E27" s="62">
+      <c r="E27" s="64">
         <v>1267</v>
       </c>
-      <c r="F27" s="62">
+      <c r="F27" s="64">
         <v>1975</v>
       </c>
-      <c r="G27" s="62">
+      <c r="G27" s="64">
         <v>2773</v>
       </c>
-      <c r="H27" s="59" t="s">
-        <v>209</v>
+      <c r="H27" s="61" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
-        <v>214</v>
+      <c r="B30" s="70" t="s">
+        <v>217</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>216</v>
-      </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
-        <v>217</v>
-      </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
+        <v>218</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>219</v>
+      </c>
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
+        <v>220</v>
+      </c>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D31" s="69" t="s">
-        <v>219</v>
-      </c>
-      <c r="E31" s="69"/>
-      <c r="F31" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
+      <c r="D31" s="71" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="71"/>
+      <c r="F31" s="72" t="s">
+        <v>223</v>
+      </c>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="68" t="s">
-        <v>221</v>
+      <c r="B32" s="70" t="s">
+        <v>224</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D32" s="69" t="s">
-        <v>222</v>
-      </c>
-      <c r="E32" s="69"/>
-      <c r="F32" s="70" t="s">
-        <v>223</v>
-      </c>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
+        <v>218</v>
+      </c>
+      <c r="D32" s="71" t="s">
+        <v>225</v>
+      </c>
+      <c r="E32" s="71"/>
+      <c r="F32" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
-        <v>224</v>
+      <c r="B33" s="70" t="s">
+        <v>227</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D33" s="69" t="s">
-        <v>225</v>
-      </c>
-      <c r="E33" s="69"/>
-      <c r="F33" s="70" t="s">
-        <v>226</v>
-      </c>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
+        <v>218</v>
+      </c>
+      <c r="D33" s="71" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="71"/>
+      <c r="F33" s="72" t="s">
+        <v>229</v>
+      </c>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="68" t="s">
-        <v>227</v>
+      <c r="B34" s="70" t="s">
+        <v>230</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D34" s="69" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="69"/>
-      <c r="F34" s="70" t="s">
-        <v>229</v>
-      </c>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
+        <v>218</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>231</v>
+      </c>
+      <c r="E34" s="71"/>
+      <c r="F34" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="68" t="s">
-        <v>230</v>
+      <c r="B35" s="70" t="s">
+        <v>233</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D35" s="69" t="s">
-        <v>231</v>
-      </c>
-      <c r="E35" s="69"/>
-      <c r="F35" s="70" t="s">
-        <v>232</v>
-      </c>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
+        <v>218</v>
+      </c>
+      <c r="D35" s="71" t="s">
+        <v>234</v>
+      </c>
+      <c r="E35" s="71"/>
+      <c r="F35" s="72" t="s">
+        <v>235</v>
+      </c>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="68" t="s">
-        <v>233</v>
+      <c r="B36" s="70" t="s">
+        <v>236</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D36" s="69" t="s">
-        <v>234</v>
-      </c>
-      <c r="E36" s="69"/>
-      <c r="F36" s="70" t="s">
-        <v>235</v>
-      </c>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
+        <v>218</v>
+      </c>
+      <c r="D36" s="71" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" s="71"/>
+      <c r="F36" s="72" t="s">
+        <v>238</v>
+      </c>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="55" t="s">
-        <v>236</v>
-      </c>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
+      <c r="C38" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
+      <c r="B40" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2718,27 +2935,27 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2" s="29">
         <f>Assumptions!B23</f>
@@ -2763,7 +2980,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2773,7 +2990,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="30">
         <f>10500*Assumptions!B23</f>
@@ -2798,7 +3015,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="30">
         <f>350*Assumptions!B23</f>
@@ -2823,7 +3040,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B4:B5)</f>
@@ -2848,7 +3065,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2858,7 +3075,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="30">
         <f>--1050*Assumptions!B23</f>
@@ -2883,7 +3100,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -2908,7 +3125,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2918,7 +3135,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" s="30">
         <f>8700*Assumptions!B23</f>
@@ -2943,7 +3160,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B11:B11)</f>
@@ -2968,7 +3185,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2978,7 +3195,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" s="30">
         <v>50000</v>
@@ -2998,7 +3215,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="30">
         <v>25000</v>
@@ -3018,7 +3235,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B14:B15)</f>
@@ -3043,7 +3260,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -3053,7 +3270,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" s="30">
         <f>500*Assumptions!B23</f>
@@ -3078,7 +3295,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B18:B18)</f>
@@ -3103,7 +3320,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" s="31">
         <f>B6+B9+B12+B16+B19</f>
@@ -3150,7 +3367,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3162,39 +3379,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4" s="26">
         <v>1</v>
@@ -3214,13 +3431,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>105</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>104</v>
       </c>
       <c r="D5" s="26">
         <v>1</v>
@@ -3240,13 +3457,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D6" s="26">
         <v>6</v>
@@ -3266,13 +3483,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>107</v>
-      </c>
       <c r="C7" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" s="26">
         <v>3</v>
@@ -3292,13 +3509,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -3318,13 +3535,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9" s="26">
         <v>1</v>
@@ -3344,7 +3561,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3356,7 +3573,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="34">
         <v>6</v>
@@ -3364,7 +3581,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="34">
         <v>13</v>
@@ -3372,7 +3589,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B14" s="35">
         <v>648000</v>
@@ -3380,7 +3597,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="35">
         <v>157200</v>
@@ -3388,7 +3605,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B16" s="35">
         <v>49572</v>
@@ -3396,7 +3613,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="35">
         <v>0</v>
@@ -3404,7 +3621,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="36">
         <v>854772</v>
@@ -3412,7 +3629,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -3422,27 +3639,27 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B22" s="30">
         <v>854772</v>
@@ -3462,7 +3679,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B23" s="37">
         <f>(1+Assumptions!B30)^0</f>
@@ -3487,7 +3704,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B24" s="38">
         <f>Assumptions!B32</f>
@@ -3508,7 +3725,7 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B25" s="31">
         <f>B22*B23*B24</f>
@@ -3558,27 +3775,27 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2" s="29">
         <f>Assumptions!B23</f>
@@ -3603,7 +3820,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3613,7 +3830,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B4" s="30">
         <f>600*Assumptions!B23</f>
@@ -3638,7 +3855,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -3663,7 +3880,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3673,7 +3890,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B7" s="30">
         <f>400*Assumptions!B23</f>
@@ -3698,7 +3915,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -3723,7 +3940,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3733,7 +3950,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B10" s="30">
         <f>8500*12</f>
@@ -3758,7 +3975,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B11" s="30">
         <f>1200*12</f>
@@ -3783,7 +4000,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B12" s="30">
         <v>12000</v>
@@ -3803,7 +4020,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B13" s="30">
         <v>8000</v>
@@ -3823,7 +4040,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B10:B13)</f>
@@ -3848,7 +4065,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -3858,7 +4075,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B16" s="30">
         <v>15000</v>
@@ -3878,7 +4095,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" s="30">
         <v>8000</v>
@@ -3898,7 +4115,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B18" s="30">
         <v>12000</v>
@@ -3918,7 +4135,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B16:B18)</f>
@@ -3943,7 +4160,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" s="31">
         <f>B5+B8+B14+B19</f>
@@ -3990,27 +4207,27 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4020,7 +4237,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="30">
         <v>34064.39316600799</v>
@@ -4040,7 +4257,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="30">
         <v>25000</v>
@@ -4060,7 +4277,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B3:B4)</f>
@@ -4110,24 +4327,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B21</f>
@@ -4152,7 +4369,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B25</f>
@@ -4227,7 +4444,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -4252,7 +4469,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -4277,7 +4494,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -4327,22 +4544,22 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4369,7 +4586,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -4379,12 +4596,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4394,7 +4611,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>3</v>
@@ -4402,71 +4619,71 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4476,27 +4693,27 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="29">
         <f>'Revenue Schedule'!B2</f>
@@ -4521,10 +4738,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="44">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
@@ -4545,27 +4762,27 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" s="30">
         <f>'Financial Model'!B2</f>
@@ -4590,7 +4807,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
@@ -4640,7 +4857,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
@@ -4665,7 +4882,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B25" s="45">
         <f>'Financial Model'!B7</f>
@@ -4690,7 +4907,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
@@ -4740,7 +4957,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4750,7 +4967,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B30" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
@@ -4775,7 +4992,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" s="44">
         <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
@@ -4800,7 +5017,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" s="44">
         <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
@@ -4825,7 +5042,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B33" s="12">
         <f>IF(B21=0,0,B25/B21)</f>
@@ -4850,7 +5067,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4860,7 +5077,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B36" s="44">
         <v>0.5675057208237986</v>
@@ -4880,7 +5097,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B37" s="44">
         <v>0.39816933638443935</v>
@@ -4900,7 +5117,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B38" s="44">
         <v>0.034324942791762014</v>
@@ -4951,13 +5168,13 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B4" s="46">
         <v>85</v>
@@ -4965,7 +5182,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="36">
         <v>1200000</v>
@@ -4973,7 +5190,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B6" s="36">
         <v>1150000</v>
@@ -4981,7 +5198,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B7" s="36">
         <v>75000</v>
@@ -4989,7 +5206,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B8" s="36">
         <v>50000</v>
@@ -4997,7 +5214,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B9" s="47">
         <v>0.8</v>
@@ -5019,185 +5236,66 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C34"/>
+  <dimension ref="B1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="10">
-        <v>4323000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="11">
-        <v>3011257</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="12">
-        <v>0.6965665047420773</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="13">
-        <v>90.1314632515668</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="14">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="16"/>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="16"/>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="16"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="16"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="16"/>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="16"/>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="16"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="17"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B34:C34"/>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B24" r:id="rId1" location="#'Assumptions'!A1"/>
-    <hyperlink ref="B25" r:id="rId2" location="#'Revenue Schedule'!A1"/>
-    <hyperlink ref="B26" r:id="rId3" location="#'Staffing &amp; Personnel'!A1"/>
-    <hyperlink ref="B27" r:id="rId4" location="#'Operating Expenses'!A1"/>
-    <hyperlink ref="B28" r:id="rId5" location="#'Capital &amp; Debt'!A1"/>
-    <hyperlink ref="B29" r:id="rId6" location="#'Financial Model'!A1"/>
-    <hyperlink ref="B30" r:id="rId7" location="#'Summary'!A1"/>
-    <hyperlink ref="B31" r:id="rId8" location="#'Prior-Year Snapshot'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BHeritage Academy&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -63,7 +63,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -582,7 +582,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -35,7 +35,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -63,7 +63,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -276,7 +276,7 @@
     <t>TUITION &amp; STUDENT FEES</t>
   </si>
   <si>
-    <t>Tuition</t>
+    <t>Gross Tuition</t>
   </si>
   <si>
     <t>Registration Fee</t>
@@ -582,7 +582,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -705,7 +705,7 @@
     <t>The model reaches net income early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -2122,7 +2122,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2132,7 +2132,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
         <v>178</v>
       </c>
@@ -2142,8 +2142,9 @@
       <c r="F2" s="42"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="50" t="s">
         <v>179</v>
       </c>
@@ -2153,6 +2154,7 @@
       <c r="F3" s="50"/>
       <c r="G3" s="50"/>
       <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
@@ -2643,7 +2645,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>213</v>
       </c>
@@ -2659,8 +2661,9 @@
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="70" t="s">
         <v>217</v>
       </c>
@@ -2676,8 +2679,9 @@
       </c>
       <c r="G30" s="72"/>
       <c r="H30" s="72"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="72"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="70" t="s">
         <v>221</v>
       </c>
@@ -2693,8 +2697,9 @@
       </c>
       <c r="G31" s="72"/>
       <c r="H31" s="72"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="72"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="70" t="s">
         <v>224</v>
       </c>
@@ -2710,8 +2715,9 @@
       </c>
       <c r="G32" s="72"/>
       <c r="H32" s="72"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="72"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="70" t="s">
         <v>227</v>
       </c>
@@ -2727,8 +2733,9 @@
       </c>
       <c r="G33" s="72"/>
       <c r="H33" s="72"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="72"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="70" t="s">
         <v>230</v>
       </c>
@@ -2744,8 +2751,9 @@
       </c>
       <c r="G34" s="72"/>
       <c r="H34" s="72"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="72"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="70" t="s">
         <v>233</v>
       </c>
@@ -2761,8 +2769,9 @@
       </c>
       <c r="G35" s="72"/>
       <c r="H35" s="72"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="72"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="70" t="s">
         <v>236</v>
       </c>
@@ -2778,6 +2787,7 @@
       </c>
       <c r="G36" s="72"/>
       <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="70" t="s">
@@ -2790,7 +2800,7 @@
       <c r="E38" s="57"/>
       <c r="F38" s="57"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="73" t="s">
         <v>240</v>
       </c>
@@ -2800,29 +2810,30 @@
       <c r="F40" s="73"/>
       <c r="G40" s="73"/>
       <c r="H40" s="73"/>
+      <c r="I40" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Private_School_+_ESA.xlsx
@@ -21,13 +21,13 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$G16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
@@ -35,7 +35,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prior-Year Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Financial Health'!$A1:$I40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Financial Health'!$A1:$I41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="254">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -426,6 +426,27 @@
     <t>Total Personnel Cost</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION</t>
+  </si>
+  <si>
+    <t>5-Year Total</t>
+  </si>
+  <si>
+    <t>Founder Compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fully-loaded (incl. benefits + payroll tax)</t>
+  </si>
+  <si>
+    <t>Founder Compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t>Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market rate ("sweat equity"). Lenders and boards underwrite to the market-rate line; the adjustment shows the gap.</t>
+  </si>
+  <si>
     <t>INSTRUCTIONAL / PROGRAM</t>
   </si>
   <si>
@@ -507,6 +528,21 @@
     <t>Cumulative Net Income</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION (memo — already in Personnel above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market ("sweat equity"). Lenders / boards underwrite to the market-rate line.</t>
+  </si>
+  <si>
     <t>Break-even</t>
   </si>
   <si>
@@ -582,7 +618,10 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
+  </si>
+  <si>
+    <t>Built from actuals</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -781,7 +820,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -879,6 +918,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
@@ -900,6 +945,13 @@
       <i/>
       <color rgb="FF6B7280"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1027,7 +1079,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1069,6 +1121,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1076,22 +1134,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1111,7 +1170,7 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1140,7 +1199,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2122,7 +2181,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I40"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2133,691 +2192,702 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="54" t="s">
+      <c r="B3" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="54" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D7" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E7" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F7" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G7" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="54" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="55">
-        <v>100</v>
-      </c>
-      <c r="D7" s="55">
-        <v>130</v>
-      </c>
-      <c r="E7" s="55">
-        <v>160</v>
-      </c>
-      <c r="F7" s="55">
-        <v>185</v>
-      </c>
-      <c r="G7" s="55">
-        <v>200</v>
+      <c r="H7" s="57" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="56">
-        <v>1975000</v>
-      </c>
-      <c r="D8" s="56">
-        <v>2612670</v>
-      </c>
-      <c r="E8" s="56">
-        <v>3286760</v>
-      </c>
-      <c r="F8" s="56">
-        <v>3895050</v>
-      </c>
-      <c r="G8" s="56">
-        <v>4323000</v>
+        <v>198</v>
+      </c>
+      <c r="C8" s="58">
+        <v>100</v>
+      </c>
+      <c r="D8" s="58">
+        <v>130</v>
+      </c>
+      <c r="E8" s="58">
+        <v>160</v>
+      </c>
+      <c r="F8" s="58">
+        <v>185</v>
+      </c>
+      <c r="G8" s="58">
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" s="56">
-        <v>854772</v>
-      </c>
-      <c r="D9" s="56">
-        <v>854772</v>
-      </c>
-      <c r="E9" s="56">
-        <v>854772</v>
-      </c>
-      <c r="F9" s="56">
-        <v>854772</v>
-      </c>
-      <c r="G9" s="56">
-        <v>854772</v>
+        <v>199</v>
+      </c>
+      <c r="C9" s="59">
+        <v>1975000</v>
+      </c>
+      <c r="D9" s="59">
+        <v>2612670</v>
+      </c>
+      <c r="E9" s="59">
+        <v>3286760</v>
+      </c>
+      <c r="F9" s="59">
+        <v>3895050</v>
+      </c>
+      <c r="G9" s="59">
+        <v>4323000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="56">
-        <v>271400</v>
-      </c>
-      <c r="D10" s="56">
-        <v>310442</v>
-      </c>
-      <c r="E10" s="56">
-        <v>351602</v>
-      </c>
-      <c r="F10" s="56">
-        <v>389506</v>
-      </c>
-      <c r="G10" s="56">
-        <v>417907</v>
+        <v>200</v>
+      </c>
+      <c r="C10" s="59">
+        <v>854772</v>
+      </c>
+      <c r="D10" s="59">
+        <v>854772</v>
+      </c>
+      <c r="E10" s="59">
+        <v>854772</v>
+      </c>
+      <c r="F10" s="59">
+        <v>854772</v>
+      </c>
+      <c r="G10" s="59">
+        <v>854772</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="56">
+        <v>17</v>
+      </c>
+      <c r="C11" s="59">
+        <v>271400</v>
+      </c>
+      <c r="D11" s="59">
+        <v>310442</v>
+      </c>
+      <c r="E11" s="59">
+        <v>351602</v>
+      </c>
+      <c r="F11" s="59">
+        <v>389506</v>
+      </c>
+      <c r="G11" s="59">
+        <v>417907</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D12" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E12" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F12" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G12" s="59">
         <v>34064.39316600799</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" s="58">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="61">
         <v>789764</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D13" s="61">
         <v>1403392</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E13" s="61">
         <v>2036322</v>
       </c>
-      <c r="F12" s="58">
+      <c r="F13" s="61">
         <v>2611708</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G13" s="61">
         <v>3011257</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="C13" s="58">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="61">
         <v>864764</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D14" s="61">
         <v>2268156</v>
       </c>
-      <c r="E13" s="58">
+      <c r="E14" s="61">
         <v>4304478</v>
       </c>
-      <c r="F13" s="58">
+      <c r="F14" s="61">
         <v>6916186</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G14" s="61">
         <v>9927443</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="59">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="60" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="62">
         <v>0.3998805063291139</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D15" s="62">
         <v>0.5371485874603376</v>
       </c>
-      <c r="E14" s="59">
+      <c r="E15" s="62">
         <v>0.6195529944382918</v>
       </c>
-      <c r="F14" s="59">
+      <c r="F15" s="62">
         <v>0.6705197622623587</v>
       </c>
-      <c r="G14" s="59">
+      <c r="G15" s="62">
         <v>0.6965665047420773</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" s="60">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="63">
         <v>19750</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D16" s="63">
         <v>20097.46153846154</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E16" s="63">
         <v>20542.25</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F16" s="63">
         <v>21054.324324324323</v>
       </c>
-      <c r="G15" s="60">
+      <c r="G16" s="63">
         <v>21615</v>
       </c>
-      <c r="H15" s="61" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="C16" s="62">
+      <c r="H16" s="64" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="65">
         <v>11602.36393166008</v>
       </c>
-      <c r="D16" s="62">
+      <c r="D17" s="65">
         <v>9225.218408969291</v>
       </c>
-      <c r="E16" s="62">
+      <c r="E17" s="65">
         <v>7752.739957287549</v>
       </c>
-      <c r="F16" s="62">
+      <c r="F17" s="65">
         <v>6909.958881978421</v>
       </c>
-      <c r="G16" s="62">
+      <c r="G17" s="65">
         <v>6533.71696583004</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="56">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="59">
         <v>600</v>
       </c>
-      <c r="D17" s="56">
+      <c r="D18" s="59">
         <v>618</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E18" s="59">
         <v>637</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F18" s="59">
         <v>656</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G18" s="59">
         <v>675</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="60">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="63">
         <v>1364</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D19" s="63">
         <v>1080.7076923076922</v>
       </c>
-      <c r="E18" s="60">
+      <c r="E19" s="63">
         <v>904.4112499999999</v>
       </c>
-      <c r="F18" s="60">
+      <c r="F19" s="63">
         <v>805.6494810810811</v>
       </c>
-      <c r="G18" s="60">
+      <c r="G19" s="63">
         <v>767.5594931</v>
       </c>
-      <c r="H18" s="61" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="63">
+      <c r="H19" s="64" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="60" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="66">
         <v>7897.64</v>
       </c>
-      <c r="D19" s="63">
+      <c r="D20" s="66">
         <v>10795.323076923078</v>
       </c>
-      <c r="E19" s="63">
+      <c r="E20" s="66">
         <v>12727.0125</v>
       </c>
-      <c r="F19" s="63">
+      <c r="F20" s="66">
         <v>14117.340540540541</v>
       </c>
-      <c r="G19" s="63">
+      <c r="G20" s="66">
         <v>15056.285</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="59">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="62">
         <v>0.4327959493670886</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D21" s="62">
         <v>0.3271641653940222</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E21" s="62">
         <v>0.26006523141330673</v>
       </c>
-      <c r="F20" s="59">
+      <c r="F21" s="62">
         <v>0.21945084145261293</v>
       </c>
-      <c r="G20" s="59">
+      <c r="G21" s="62">
         <v>0.1977265787647467</v>
       </c>
-      <c r="H20" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="C21" s="59">
+      <c r="H21" s="64" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="C22" s="62">
         <v>0.0690632911392405</v>
       </c>
-      <c r="D21" s="59">
+      <c r="D22" s="62">
         <v>0.053773342978638713</v>
       </c>
-      <c r="E21" s="59">
+      <c r="E22" s="62">
         <v>0.04402688361790943</v>
       </c>
-      <c r="F21" s="59">
+      <c r="F22" s="62">
         <v>0.038265273616513266</v>
       </c>
-      <c r="G21" s="59">
+      <c r="G22" s="62">
         <v>0.0355105016470044</v>
       </c>
-      <c r="H21" s="61" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="59">
+      <c r="H22" s="64" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="62">
         <v>0.42978632911392406</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D23" s="62">
         <v>0.5540140928628567</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E23" s="62">
         <v>0.6329595102775986</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F23" s="62">
         <v>0.6805489018112733</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G23" s="62">
         <v>0.7056028221142725</v>
       </c>
-      <c r="H22" s="61" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="C23" s="64">
+      <c r="H23" s="64" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="67">
         <v>4</v>
       </c>
-      <c r="D23" s="64">
+      <c r="D24" s="67">
         <v>4</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E24" s="67">
         <v>4</v>
       </c>
-      <c r="F23" s="64">
+      <c r="F24" s="67">
         <v>4</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G24" s="67">
         <v>4</v>
       </c>
-      <c r="H23" s="61" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="C24" s="65">
+      <c r="H24" s="64" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" s="68">
         <v>24.918336160088252</v>
       </c>
-      <c r="D24" s="65">
+      <c r="D25" s="68">
         <v>42.49175944353473</v>
       </c>
-      <c r="E24" s="65">
+      <c r="E25" s="68">
         <v>61.07215795277884</v>
       </c>
-      <c r="F24" s="65">
+      <c r="F25" s="68">
         <v>77.81650437986194</v>
       </c>
-      <c r="G24" s="65">
+      <c r="G25" s="68">
         <v>89.54573137806075</v>
       </c>
-      <c r="H24" s="61" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
-        <v>207</v>
-      </c>
-      <c r="C25" s="40" t="str">
+      <c r="H25" s="64" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="42" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="66" t="str">
+      <c r="D26" s="69" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="66" t="str">
+      <c r="E26" s="69" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="66" t="str">
+      <c r="F26" s="69" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="66" t="str">
+      <c r="G26" s="69" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="61" t="s">
+      <c r="H26" s="64" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
-        <v>208</v>
-      </c>
-      <c r="C26" s="67">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="60" t="s">
+        <v>221</v>
+      </c>
+      <c r="C27" s="70">
         <v>9</v>
       </c>
-      <c r="D26" s="68">
+      <c r="D27" s="71">
         <v>23</v>
       </c>
-      <c r="E26" s="64">
+      <c r="E27" s="67">
         <v>42</v>
       </c>
-      <c r="F26" s="69" t="s">
-        <v>209</v>
-      </c>
-      <c r="G26" s="69" t="s">
-        <v>209</v>
-      </c>
-      <c r="H26" s="61" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
-        <v>211</v>
-      </c>
-      <c r="C27" s="64">
+      <c r="F27" s="72" t="s">
+        <v>222</v>
+      </c>
+      <c r="G27" s="72" t="s">
+        <v>222</v>
+      </c>
+      <c r="H27" s="64" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="60" t="s">
+        <v>224</v>
+      </c>
+      <c r="C28" s="67">
         <v>272</v>
       </c>
-      <c r="D27" s="64">
+      <c r="D28" s="67">
         <v>690</v>
       </c>
-      <c r="E27" s="64">
+      <c r="E28" s="67">
         <v>1267</v>
       </c>
-      <c r="F27" s="64">
+      <c r="F28" s="67">
         <v>1975</v>
       </c>
-      <c r="G27" s="64">
+      <c r="G28" s="67">
         <v>2773</v>
       </c>
-      <c r="H27" s="61" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="70" t="s">
-        <v>217</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D30" s="71" t="s">
-        <v>219</v>
-      </c>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72" t="s">
-        <v>220</v>
-      </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
+      <c r="H28" s="64" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="70" t="s">
-        <v>221</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D31" s="71" t="s">
-        <v>222</v>
-      </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="72" t="s">
-        <v>223</v>
-      </c>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
+      <c r="B31" s="73" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D31" s="74" t="s">
+        <v>232</v>
+      </c>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D32" s="71" t="s">
-        <v>225</v>
-      </c>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72" t="s">
-        <v>226</v>
-      </c>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
+      <c r="B32" s="73" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="74" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="74"/>
+      <c r="F32" s="75" t="s">
+        <v>236</v>
+      </c>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="70" t="s">
-        <v>227</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D33" s="71" t="s">
-        <v>228</v>
-      </c>
-      <c r="E33" s="71"/>
-      <c r="F33" s="72" t="s">
-        <v>229</v>
-      </c>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
+      <c r="B33" s="73" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" s="74" t="s">
+        <v>238</v>
+      </c>
+      <c r="E33" s="74"/>
+      <c r="F33" s="75" t="s">
+        <v>239</v>
+      </c>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="70" t="s">
-        <v>230</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D34" s="71" t="s">
+      <c r="B34" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="71"/>
-      <c r="F34" s="72" t="s">
-        <v>232</v>
-      </c>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
+      <c r="D34" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" s="74"/>
+      <c r="F34" s="75" t="s">
+        <v>242</v>
+      </c>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="75"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="70" t="s">
-        <v>233</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D35" s="71" t="s">
-        <v>234</v>
-      </c>
-      <c r="E35" s="71"/>
-      <c r="F35" s="72" t="s">
-        <v>235</v>
-      </c>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
+      <c r="B35" s="73" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D35" s="74" t="s">
+        <v>244</v>
+      </c>
+      <c r="E35" s="74"/>
+      <c r="F35" s="75" t="s">
+        <v>245</v>
+      </c>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="75"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="70" t="s">
-        <v>236</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D36" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="E36" s="71"/>
-      <c r="F36" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="70" t="s">
+      <c r="B36" s="73" t="s">
+        <v>246</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D36" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="E36" s="74"/>
+      <c r="F36" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+    </row>
+    <row r="37" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="73" t="s">
+        <v>249</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" s="74" t="s">
+        <v>250</v>
+      </c>
+      <c r="E37" s="74"/>
+      <c r="F37" s="75" t="s">
+        <v>251</v>
+      </c>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="73" t="s">
-        <v>240</v>
-      </c>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
+      <c r="C39" s="60" t="s">
+        <v>252</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
@@ -2832,95 +2902,97 @@
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:I36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B41:I41"/>
   </mergeCells>
-  <conditionalFormatting sqref="C12:G12">
+  <conditionalFormatting sqref="C13:G13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C12&gt;=0</formula>
+      <formula>C13&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C12&gt;=-1</formula>
+      <formula>C13&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C12&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:G13">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C13&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C13&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C13&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:G14">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C14&gt;=0.05</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>C14&gt;=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C14&lt;0</formula>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C14&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C14&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C15&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C15&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C15&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&gt;=10000</formula>
+      <formula>C16&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&gt;=7000</formula>
+      <formula>C16&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&lt;7000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C21&lt;=0.55</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C21&lt;=0.65</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C21&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:G22">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C22&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C22&lt;=0.22</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C22&gt;0.22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:G23">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C23&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C25:G25">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C25&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1.15</formula>
+      <formula>C25&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1.15</formula>
+      <formula>C25&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3369,11 +3441,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3759,9 +3831,154 @@
         <v>854772</v>
       </c>
     </row>
+    <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="30">
+        <v>95000</v>
+      </c>
+      <c r="C28" s="30">
+        <v>95000</v>
+      </c>
+      <c r="D28" s="30">
+        <v>95000</v>
+      </c>
+      <c r="E28" s="30">
+        <v>95000</v>
+      </c>
+      <c r="F28" s="30">
+        <v>95000</v>
+      </c>
+      <c r="G28" s="30">
+        <f>SUM(B28:F28)</f>
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="30">
+        <v>126018</v>
+      </c>
+      <c r="C29" s="30">
+        <v>126018</v>
+      </c>
+      <c r="D29" s="30">
+        <v>126018</v>
+      </c>
+      <c r="E29" s="30">
+        <v>126018</v>
+      </c>
+      <c r="F29" s="30">
+        <v>126018</v>
+      </c>
+      <c r="G29" s="30">
+        <f>SUM(B29:F29)</f>
+        <v>630090</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="30">
+        <v>140000</v>
+      </c>
+      <c r="C30" s="30">
+        <v>140000</v>
+      </c>
+      <c r="D30" s="30">
+        <v>180000</v>
+      </c>
+      <c r="E30" s="30">
+        <v>180000</v>
+      </c>
+      <c r="F30" s="30">
+        <v>180000</v>
+      </c>
+      <c r="G30" s="30">
+        <f>SUM(B30:F30)</f>
+        <v>820000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="30">
+        <v>185710</v>
+      </c>
+      <c r="C31" s="30">
+        <v>185710</v>
+      </c>
+      <c r="D31" s="30">
+        <v>238770</v>
+      </c>
+      <c r="E31" s="30">
+        <v>238770</v>
+      </c>
+      <c r="F31" s="30">
+        <v>238770</v>
+      </c>
+      <c r="G31" s="30">
+        <f>SUM(B31:F31)</f>
+        <v>1087730</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="10">
+        <v>59693</v>
+      </c>
+      <c r="C32" s="10">
+        <v>59693</v>
+      </c>
+      <c r="D32" s="10">
+        <v>112753</v>
+      </c>
+      <c r="E32" s="10">
+        <v>112753</v>
+      </c>
+      <c r="F32" s="10">
+        <v>112753</v>
+      </c>
+      <c r="G32" s="10">
+        <f>SUM(B32:F32)</f>
+        <v>457645</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A33:G33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3831,7 +4048,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3841,7 +4058,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B4" s="30">
         <f>600*Assumptions!B23</f>
@@ -3866,7 +4083,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -3891,7 +4108,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3901,7 +4118,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B7" s="30">
         <f>400*Assumptions!B23</f>
@@ -3926,7 +4143,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -3951,7 +4168,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3961,7 +4178,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B10" s="30">
         <f>8500*12</f>
@@ -3986,7 +4203,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B11" s="30">
         <f>1200*12</f>
@@ -4011,7 +4228,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B12" s="30">
         <v>12000</v>
@@ -4031,7 +4248,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B13" s="30">
         <v>8000</v>
@@ -4051,7 +4268,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B10:B13)</f>
@@ -4076,7 +4293,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4086,7 +4303,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B16" s="30">
         <v>15000</v>
@@ -4106,7 +4323,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B17" s="30">
         <v>8000</v>
@@ -4126,7 +4343,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B18" s="30">
         <v>12000</v>
@@ -4146,7 +4363,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B16:B18)</f>
@@ -4171,7 +4388,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B21" s="31">
         <f>B5+B8+B14+B19</f>
@@ -4238,7 +4455,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4248,7 +4465,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B3" s="30">
         <v>34064.39316600799</v>
@@ -4268,7 +4485,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B4" s="30">
         <v>25000</v>
@@ -4288,7 +4505,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B3:B4)</f>
@@ -4326,11 +4543,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4355,7 +4572,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B21</f>
@@ -4380,7 +4597,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B25</f>
@@ -4455,7 +4672,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -4480,7 +4697,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -4505,7 +4722,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -4532,48 +4749,147 @@
       <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="41">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>7.996017670742367</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="41">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>21.763293469326324</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="41">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>40.58876649621972</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="41">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>63.969099429458396</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="41">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>90.1314632515668</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="41" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="30">
+        <v>126018</v>
+      </c>
+      <c r="C12" s="30">
+        <v>126018</v>
+      </c>
+      <c r="D12" s="30">
+        <v>126018</v>
+      </c>
+      <c r="E12" s="30">
+        <v>126018</v>
+      </c>
+      <c r="F12" s="30">
+        <v>126018</v>
+      </c>
+      <c r="G12" s="30">
+        <f>SUM(B12:F12)</f>
+        <v>630090</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="30">
+        <v>185710</v>
+      </c>
+      <c r="C13" s="30">
+        <v>185710</v>
+      </c>
+      <c r="D13" s="30">
+        <v>238770</v>
+      </c>
+      <c r="E13" s="30">
+        <v>238770</v>
+      </c>
+      <c r="F13" s="30">
+        <v>238770</v>
+      </c>
+      <c r="G13" s="30">
+        <f>SUM(B13:F13)</f>
+        <v>1087730</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" s="10">
+        <v>59693</v>
+      </c>
+      <c r="C14" s="10">
+        <v>59693</v>
+      </c>
+      <c r="D14" s="10">
+        <v>112753</v>
+      </c>
+      <c r="E14" s="10">
+        <v>112753</v>
+      </c>
+      <c r="F14" s="10">
+        <v>112753</v>
+      </c>
+      <c r="G14" s="10">
+        <f>SUM(B14:F14)</f>
+        <v>457645</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D16" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E16" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F16" s="43" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4596,18 +4912,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>157</v>
+      <c r="A2" s="45" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4689,12 +5005,12 @@
         <v>42</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4749,24 +5065,24 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="44">
+        <v>173</v>
+      </c>
+      <c r="C18" s="46">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.3</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="46">
         <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="46">
         <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.15625</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="46">
         <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.08108108108108109</v>
       </c>
@@ -4793,7 +5109,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B21" s="30">
         <f>'Financial Model'!B2</f>
@@ -4818,7 +5134,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
@@ -4868,7 +5184,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
@@ -4893,32 +5209,32 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="B25" s="45">
+        <v>159</v>
+      </c>
+      <c r="B25" s="47">
         <f>'Financial Model'!B7</f>
         <v>789764</v>
       </c>
-      <c r="C25" s="45">
+      <c r="C25" s="47">
         <f>'Financial Model'!C7</f>
         <v>1403392</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="47">
         <f>'Financial Model'!D7</f>
         <v>2036322</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="47">
         <f>'Financial Model'!E7</f>
         <v>2611708</v>
       </c>
-      <c r="F25" s="45">
+      <c r="F25" s="47">
         <f>'Financial Model'!F7</f>
         <v>3011257</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
@@ -4968,7 +5284,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4978,7 +5294,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B30" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
@@ -5003,57 +5319,57 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B31" s="44">
+        <v>176</v>
+      </c>
+      <c r="B31" s="46">
         <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
         <v>0.4327959493670886</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="46">
         <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
         <v>0.3271641653940222</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="46">
         <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
         <v>0.26006523141330673</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="46">
         <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
         <v>0.21945084145261293</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="46">
         <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
         <v>0.1977265787647467</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B32" s="44">
+        <v>177</v>
+      </c>
+      <c r="B32" s="46">
         <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.13741772151898735</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="46">
         <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.11882174174312102</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="46">
         <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.10697525830909467</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="46">
         <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.10000025673611379</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="46">
         <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.0966705991209808</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B33" s="12">
         <f>IF(B21=0,0,B25/B21)</f>
@@ -5078,7 +5394,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -5088,61 +5404,61 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B36" s="44">
+        <v>180</v>
+      </c>
+      <c r="B36" s="46">
         <v>0.5675057208237986</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="46">
         <v>0.5732777238345675</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="46">
         <v>0.5768052612509744</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="46">
         <v>0.5789280554886744</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="46">
         <v>0.5801743191959632</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" s="44">
+        <v>181</v>
+      </c>
+      <c r="B37" s="46">
         <v>0.39816933638443935</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="46">
         <v>0.4025342174644695</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="46">
         <v>0.4053534765757952</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="46">
         <v>0.4071812549774971</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="46">
         <v>0.4083573126485675</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="44">
+        <v>182</v>
+      </c>
+      <c r="B38" s="46">
         <v>0.034324942791762014</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="46">
         <v>0.02418805870096303</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="46">
         <v>0.01784126217323042</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="46">
         <v>0.01389068953382846</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="46">
         <v>0.01146836815546937</v>
       </c>
     </row>
@@ -5179,21 +5495,21 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="46">
+        <v>184</v>
+      </c>
+      <c r="B4" s="48">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B5" s="36">
         <v>1200000</v>
@@ -5201,7 +5517,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B6" s="36">
         <v>1150000</v>
@@ -5209,7 +5525,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B7" s="36">
         <v>75000</v>
@@ -5217,7 +5533,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B8" s="36">
         <v>50000</v>
@@ -5225,9 +5541,9 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="47">
+        <v>187</v>
+      </c>
+      <c r="B9" s="49">
         <v>0.8</v>
       </c>
     </row>
@@ -5275,26 +5591,26 @@
       <c r="H1" s="18"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="B2" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
+      <c r="B4" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="3">
